--- a/Excel/7_RiceCultivation_WIP_v02.prename.bak.xlsx
+++ b/Excel/7_RiceCultivation_WIP_v02.prename.bak.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90E703FA-A949-4B7B-BE7C-F0A90A85B3DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF755126-83E1-4668-B5BA-B89C99D2F398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1755" yWindow="1020" windowWidth="36255" windowHeight="19140" activeTab="4" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="28800" windowHeight="15345" firstSheet="3" activeTab="7" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -20,8 +20,11 @@
     <sheet name="Input - Rice" sheetId="70" r:id="rId5"/>
     <sheet name="7.1.1-2 Rice cultivation" sheetId="69" r:id="rId6"/>
     <sheet name="Constants - Rice cultivation" sheetId="110" r:id="rId7"/>
-    <sheet name="Constants - Common" sheetId="119" r:id="rId8"/>
+    <sheet name="Constants - Common" sheetId="120" r:id="rId8"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId9"/>
+  </externalReferences>
   <definedNames>
     <definedName name="AgResidues_Equations_Leaching.VEERG_6_3_1_1__1__LeachingAndRunoffEmissionsCropAndPastureResidue">_xlfn.LAMBDA(_xlpm.Mleachcp,_xlpm.EFleach,_xlpm.CgN2O, _xlpm.Mleachcp * _xlpm.EFleach * _xlpm.CgN2O * 10 ^ (-3))</definedName>
     <definedName name="AgResidues_Equations_Leaching.VEERG_6_3_1_1__1__LeachingAndRunoffEmissionsCropAndPastureResidue_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(5, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Mleachcp","mass of nitrogen lost through leaching and runoff from the crop residue c or pasture residue p (kg N)";"EFleach","emission factor for leaching and runoff (kg N2O-N/kg N)";"CgN2O","factor to convert elemental mass of nitrous oxide to molecular mass (dimensionless)";"c","Crop residue type";"p","Pasture residue type"}, _xlpm.r, _xlpm.c))))</definedName>
@@ -194,6 +197,7 @@
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Unit">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Variable">_xlfn.LAMBDA("")</definedName>
     <definedName name="Common_SourceData.Common_SourceData_WetAndDryZones_Variation">_xlfn.LAMBDA(_xlfn.MAKEARRAY(3, 1, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"VARIATION OF SOURCE DATA:";"Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.";"Fixed typo - Changed 'Fry' to 'Dry'."}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="Common_SourceData_DensityOfMethane_Data">'Constants - Common'!$D$175</definedName>
     <definedName name="CommonCropping_SourceData.CommonCropping_SourceData_FracGASFfInorganicFertiliser_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(6, 3, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Fertiliser type f","FracGASFf","Basis";"Urea-based fertilisers",0.15,"Urea";"Ammonium-based fertilisers",0.08,"Ammonium";"Nitrate-based fertilisers",0.01,"Nitrate";"Ammonium-nitrate based fertilisers",0.05,"Ammonium-nitrate";"Other fertilisers",0.11,"Other"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="CommonCropping_SourceData.CommonCropping_SourceData_FracGASFfInorganicFertiliser_NIRReference">_xlfn.LAMBDA("IPCC 2019 Refinement Volume 4 Table 11.3 [1, p. 11]")</definedName>
     <definedName name="CommonCropping_SourceData.CommonCropping_SourceData_FracGASFfInorganicFertiliser_Source">_xlfn.LAMBDA("VEERG 2026:Table 12.2.2.9")</definedName>
@@ -2360,126 +2364,6 @@
   <dxfs count="66">
     <dxf>
       <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -3339,6 +3223,126 @@
         <patternFill patternType="none">
           <fgColor indexed="64"/>
           <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -7030,6 +7034,26 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Home"/>
+      <sheetName val="Constants - Common"/>
+      <sheetName val="Acknowledgements"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
 <rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
   <global>
@@ -7119,12 +7143,12 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6C986F30-D9EC-4803-8DA0-95980EFC62A0}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{BF8C5BCB-4DC8-4430-B959-432306869E90}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
   <autoFilter ref="D20:D30" xr:uid="{5FA81339-C6C8-4D36-BEEA-6C4AEDD9E676}">
     <filterColumn colId="0" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{DB52865D-6F2D-4651-9C10-87FA05E28EDB}" name="SA 4 Name">
+    <tableColumn id="1" xr3:uid="{F763B76B-32BA-4AAD-B19F-19E095F8448D}" name="SA 4 Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7133,16 +7157,16 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{CE5A8FF1-51D1-4DC7-A67C-E1BB1D169339}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{89838C81-0EF9-443A-A9A0-89573C017402}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
   <autoFilter ref="D36:E43" xr:uid="{B8E87A66-3E41-4AD3-925D-01EE21B43D7A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{DE7AB944-8934-40CD-9BD0-1EB0965AAF53}" name="Gas">
+    <tableColumn id="1" xr3:uid="{4A66C79B-A8A3-4AFA-A722-7610686CB076}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{BF74DAA5-1727-4598-8BDF-A1FFEAF36797}" name="CO2-e factor">
+    <tableColumn id="2" xr3:uid="{B4E20F99-96C3-499E-A196-8F761371D0D9}" name="CO2-e factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7151,7 +7175,7 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{84EB336F-AD27-4469-81D9-D75BF392704A}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{DC56238C-EC55-49B0-882F-2CF5F944E96B}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
   <autoFilter ref="D47:H54" xr:uid="{C1F562BB-DAA6-45BB-951A-7BAFA5B64B45}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -7160,19 +7184,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{6FF8E719-A496-4146-95F1-5C74FB0907DF}" name="Gas">
+    <tableColumn id="1" xr3:uid="{888594FC-3A79-4584-9695-B0220220F7EA}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{141A87B3-BDC7-4BC9-86AA-9AEF8E4516F0}" name="Conversion factor">
+    <tableColumn id="5" xr3:uid="{1D293FD3-3374-4336-A222-9D7EC1AF68B8}" name="Conversion factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{6EEA02FE-9CA9-42CC-9715-CE1AE379A798}" name="Conversion factor 1">
+    <tableColumn id="2" xr3:uid="{7CA1A532-A9CE-4133-A24A-1C7B197B5F35}" name="Conversion factor 1">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{63DBA7EA-762D-4502-893E-4F59C65F1D06}" name="Conversion factor 2">
+    <tableColumn id="3" xr3:uid="{B1546960-5275-4CEB-AB35-2DEF1439E361}" name="Conversion factor 2">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{D45503ED-E349-402E-BE70-522640844EB2}" name="Conversion factor combined">
+    <tableColumn id="4" xr3:uid="{3CEA96CE-452F-437D-8013-BFFBCDB3F864}" name="Conversion factor combined">
       <calculatedColumnFormula>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7181,7 +7205,7 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{B64F6EE9-601E-431C-889B-F490F94AAF6D}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{BF6FBD55-90AE-4942-97CF-6D39CB689197}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
   <autoFilter ref="D89:S97" xr:uid="{5A437AE9-7724-4CF2-ACCF-291078682FB9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -7201,52 +7225,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{E3EAE8D7-79F7-4CFF-AA60-81BEB0D1F996}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{D01C89B8-460D-43FB-BC13-860F40EEDF57}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{90558006-D3B7-45CA-BB08-CBC5FB2D525E}" name="MAT" totalsRowDxfId="47" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{D69D2743-DE4D-4C2E-897F-A682E4792E90}" name="MAT" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{31536C54-9D90-4BA1-8630-5A5825932E3D}" name="MAP" totalsRowDxfId="46" totalsRowCellStyle="Content bold">
+    <tableColumn id="3" xr3:uid="{43E94A14-ECA9-4D24-BD3B-6F90853F1623}" name="MAP" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{C736DFB1-216D-41C0-9BDA-AF1DACA0D28E}" name="Frost days per year" totalsRowDxfId="45" totalsRowCellStyle="Content bold">
+    <tableColumn id="4" xr3:uid="{0FFE5CEB-92B8-4F0C-954C-1654258B9009}" name="Frost days per year" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{EBC9733B-D9D6-44EF-92E6-EAE63368707E}" name="Elevation" totalsRowDxfId="44" totalsRowCellStyle="Content bold">
+    <tableColumn id="5" xr3:uid="{EAE0BFB1-8A8D-4F76-AF2F-7F3A3F39AF16}" name="Elevation" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{86BD24B4-BCF5-43E4-9791-66486A239A29}" name="MAP:PET" totalsRowDxfId="43" totalsRowCellStyle="Content bold">
+    <tableColumn id="6" xr3:uid="{7BF56A54-DEFF-4963-B9D8-1425EB5F5986}" name="MAP:PET" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{04625927-EE66-47A4-9B56-E9FF16A40381}" name="Min temp" totalsRowDxfId="42" totalsRowCellStyle="Content bold">
+    <tableColumn id="7" xr3:uid="{D894A124-2A58-4A9A-81F0-270403516E8D}" name="Min temp" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{0B6D7849-AF37-4F92-B3BC-F00F938473A4}" name="Max temp" totalsRowDxfId="41" totalsRowCellStyle="Content bold">
+    <tableColumn id="8" xr3:uid="{281E5491-0322-4B39-91C1-808A9AA92DC9}" name="Max temp" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{79B2D447-365C-4E5B-9B46-EB9A6FEABC8F}" name="Min rainfall" totalsRowDxfId="40" totalsRowCellStyle="Content bold">
+    <tableColumn id="9" xr3:uid="{549BB998-F7AA-41DD-9CD1-2547B6B5AE4E}" name="Min rainfall" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{15AE00CB-0DCC-4C76-9A69-811B2102ABD0}" name="Max rainfall" totalsRowDxfId="39" totalsRowCellStyle="Content bold">
+    <tableColumn id="10" xr3:uid="{29334872-89CD-401E-ABA5-8B865307D169}" name="Max rainfall" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{453B192C-DCF9-4759-9B4F-A3C3978C4EAF}" name="Min frost days" totalsRowDxfId="38" totalsRowCellStyle="Content bold">
+    <tableColumn id="11" xr3:uid="{34F87F29-D818-4C04-94C8-67D9646FCEA8}" name="Min frost days" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{399D591D-E030-4FE8-8A4D-14B154F55401}" name="Max frost days" totalsRowDxfId="37" totalsRowCellStyle="Content bold">
+    <tableColumn id="15" xr3:uid="{BD42682C-5957-4823-B606-9612A785CCDC}" name="Max frost days" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{7BB2477B-60BA-4ACB-81E8-FD8FE87495FF}" name="Min elevation" totalsRowDxfId="36" totalsRowCellStyle="Content bold">
+    <tableColumn id="12" xr3:uid="{82F25CB4-1EDC-46ED-8292-E152A1B2E2EF}" name="Min elevation" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{0A47AD04-56FF-4DD7-A870-3813EAA5B320}" name="Max elevation" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
+    <tableColumn id="16" xr3:uid="{B18A08B2-51EC-46CB-B531-47382F39C7F5}" name="Max elevation" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{FE9A6C0E-201D-4A67-8D4D-C6A488CA05EA}" name="Min MAP:PET" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
+    <tableColumn id="13" xr3:uid="{0C71510E-74B2-4C70-BF53-A6CFF373D454}" name="Min MAP:PET" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{3378CC43-2399-435F-A3FE-BB19D039E80F}" name="Max MAP:PET" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
+    <tableColumn id="17" xr3:uid="{C9B72C4B-BEDC-4438-867D-26385A49C0C7}" name="Max MAP:PET" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7255,16 +7279,16 @@
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{0D035090-ADB1-4F10-9C19-A48DE1D5960D}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{F3B17F77-0B3A-4426-93C3-BED583E09013}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
   <autoFilter ref="D63:E77" xr:uid="{3597E019-B21E-4B76-BCC8-D02D497BCFA9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{1ECE3957-9413-4408-BDB8-77552A7231E8}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{0A9FF53A-8FDB-433E-8F42-964A381B2029}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{03FFA737-2FA7-48E9-A115-73FA50C9393D}" name="Wet or Dry Zone" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{DF0F466D-B512-4631-8BDE-9FCCEFF29E7F}" name="Wet or Dry Zone" totalsRowDxfId="20" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7273,7 +7297,7 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{BEF50EEC-58C1-4511-A309-1BA0389F0DBD}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{7C6F3031-7FEF-43AA-963A-FBBC39238103}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
   <autoFilter ref="D109:G112" xr:uid="{AB16FEAB-AB03-45E1-BBD4-66D29CD412DF}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -7281,16 +7305,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{FCB9DB5A-F79A-4195-A2D3-345C295DFC8A}" name="Temperature Zone">
+    <tableColumn id="1" xr3:uid="{39EE17B2-75E6-4B6B-9A57-63C3028B3EE6}" name="Temperature Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{25D74762-0A2D-4400-B824-894D618905BB}" name="MAT">
+    <tableColumn id="2" xr3:uid="{CCB2E66E-AD6F-420D-9AF6-B3E07D8D74EF}" name="MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{1205EC90-4A04-43FC-A053-69E387CE1D3F}" name="Min MAT">
+    <tableColumn id="3" xr3:uid="{6F1CB18C-DF38-488E-B3E2-34C2F8709AA1}" name="Min MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{A0CC6FD8-F8F6-4A79-9CDF-BE796852DAF1}" name="Max MAT">
+    <tableColumn id="4" xr3:uid="{DABCD947-495C-4C96-810B-4CB3713B73FF}" name="Max MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7299,7 +7323,7 @@
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{356F1A3E-799D-40CF-8D17-7ECCC24A8932}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="33" xr:uid="{944DE6B8-4338-4BE5-979C-1791AD58CCA0}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
   <autoFilter ref="D119:G121" xr:uid="{E08772F3-2E8C-40A8-B755-08A5BBDF4130}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -7307,16 +7331,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{F2FCA308-B091-442E-94CA-E0A51124F1E1}" name="Rainfall Zone">
+    <tableColumn id="1" xr3:uid="{9F55B56B-689E-4737-B787-F913DEF27C75}" name="Rainfall Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{71D5D2C7-753E-4961-91F7-5D8FD4EBBBB8}" name="Annual rainfall">
+    <tableColumn id="2" xr3:uid="{DC0A47B4-EA07-48B0-9434-AD296A35AEDE}" name="Annual rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{6FA6F6A2-93E0-4091-A742-AE671B909E65}" name="Min rainfall">
+    <tableColumn id="3" xr3:uid="{54C0FC4D-0BA9-4CA9-A036-3D88255467F7}" name="Min rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{EBBE1093-D022-42FA-A758-FE815C9D665B}" name="Max rainfall">
+    <tableColumn id="4" xr3:uid="{CD27D80F-1F72-496F-8E02-533C46124C84}" name="Max rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7325,16 +7349,16 @@
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{C2C58793-EC57-49E4-811D-88A2C42FD549}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="34" xr:uid="{B9E67874-D230-4FFB-84B3-A3DD5CEFA594}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
   <autoFilter ref="D127:E129" xr:uid="{A159E140-02ED-4547-B6E1-6695D8B16A11}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{8DEDD535-7F20-4744-95AD-A4D8DE59C041}" name="Leaching Zone">
+    <tableColumn id="1" xr3:uid="{A1585D6D-DDCD-4303-ADF0-CF5C1A382EC3}" name="Leaching Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{413AA76F-C255-42F1-A6D5-5CD24BBBAF26}" name="Leaching criteria">
+    <tableColumn id="2" xr3:uid="{656C4A4F-C769-452B-B16C-ECB6D98F268D}" name="Leaching criteria">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7343,16 +7367,16 @@
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{99111242-9C75-4E29-97AB-7B805B522700}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="35" xr:uid="{1C5B1D03-D274-4731-89BE-7D9DED9D50CB}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
   <autoFilter ref="D153:E158" xr:uid="{133D42B0-F6D2-470A-858A-37E6A7F5EC2B}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{BDB9D991-F5EB-4B03-9F51-46A4472289C1}" name="Data source">
+    <tableColumn id="1" xr3:uid="{D1FACA62-4486-4C39-AE16-2EDBB736D7CF}" name="Data source">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{01E97336-A13E-4773-A06E-95DCCDC3855D}" name="Data score">
+    <tableColumn id="2" xr3:uid="{0CCD7813-2473-4B70-95DB-B8DA2536FFD2}" name="Data score">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7361,16 +7385,16 @@
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{2F5DAA02-E4E8-4624-A2C5-096D1B60A921}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="36" xr:uid="{84168837-9254-43AB-9675-9F0776713ED8}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
   <autoFilter ref="D134:E136" xr:uid="{308E99BE-FE1F-47A4-B2CA-97217277C4E9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{1FF542F2-F612-45D7-AC03-2F170C811D2C}" name="Is in leaching zone">
+    <tableColumn id="1" xr3:uid="{00936C20-2EF3-4B92-B727-606367DF7072}" name="Is in leaching zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{CAF3234F-1744-4CC7-97FB-29E26283D105}" name="FracWET" dataDxfId="31">
+    <tableColumn id="2" xr3:uid="{5827BEB9-27F5-4E79-98F3-336C5F4D89BD}" name="FracWET" dataDxfId="19">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7403,7 +7427,7 @@
 </file>
 
 <file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{7C4B023C-39DC-4A61-B287-ACF14E1CC6BC}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="37" xr:uid="{DC64BB62-ACC0-447A-AEA6-9465412C91CC}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
   <autoFilter ref="D186:H199" xr:uid="{D41FBEA4-8379-4DF7-A068-BF94D364F1A2}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -7412,19 +7436,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{08E69A42-D0D6-4FBD-91D3-EC4843CB8995}" name="Production system j">
+    <tableColumn id="1" xr3:uid="{6BBBAD5E-8ED5-45E8-85B7-C87C1EDAE39A}" name="Production system j">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{FB6F1229-41A4-4698-ADAF-85A7F3BDC850}" name="EFN2O">
+    <tableColumn id="2" xr3:uid="{A08D22BD-E92E-497B-AAB7-1E3610756D8B}" name="EFN2O">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{48F26286-FAFA-4819-9AFA-F6ECAE3F6B49}" name="Production system only">
+    <tableColumn id="3" xr3:uid="{4D245E98-DE9A-4026-906B-0DCCACBE5B17}" name="Production system only">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{99A2A834-E5E1-4659-9E7A-BC2543C1E44F}" name="Irrigation method">
+    <tableColumn id="4" xr3:uid="{3C57EBF6-49F2-4557-92A5-992B2F31B453}" name="Irrigation method">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{4316727C-0C8D-4A2E-947B-24A6E48379FF}" name="Rainfall zone">
+    <tableColumn id="5" xr3:uid="{A42A5612-2A9C-46A0-8D8F-2359A8948938}" name="Rainfall zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7433,16 +7457,16 @@
 </file>
 
 <file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="26" xr:uid="{8771BEDC-DFB7-49CC-BFDB-089589025B03}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="38" xr:uid="{03B2CDD8-3520-4B47-8A98-730FF87B5CC0}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
   <autoFilter ref="D142:E147" xr:uid="{1F48CA34-50DE-46D5-B32A-BB3A1E818E37}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{0349773D-F8B1-4F20-8D67-02CFFC1D5B01}" name="Irrigation type i">
+    <tableColumn id="1" xr3:uid="{8E925759-33F1-48CE-BF8F-1C907D56D334}" name="Irrigation type i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{E1A81332-451C-4F13-819A-08B47B324E1A}" name="FracWET" dataDxfId="30" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{2339A0A8-282A-4C1D-88CC-C91D7F7E2F90}" name="FracWET" dataDxfId="18" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7451,16 +7475,16 @@
 </file>
 
 <file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{0B56AF9D-3A20-46F2-9DF6-908E16C583F9}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="39" xr:uid="{7D9B35D3-DA52-4C11-91F1-92D652B8FE4E}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
   <autoFilter ref="D206:E208" xr:uid="{D5BE3F89-D70E-4C53-A71C-E756622DEF38}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{19ECEEA9-A0E2-448E-9242-5EB4612E5A30}" name="Climate zone">
+    <tableColumn id="1" xr3:uid="{D5BFF976-4AC1-486A-AC18-2703A0371049}" name="Climate zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{D5BC812F-1B20-433B-A220-45B290E585E4}" name="EFPRP" dataDxfId="29" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{015C7263-11EF-4ECD-9A95-0D1FA0C0AB59}" name="EFPRP" dataDxfId="17" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7469,16 +7493,16 @@
 </file>
 
 <file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="28" xr:uid="{9254172A-1F0A-4DA8-AF3D-FBD2D01D814B}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="40" xr:uid="{ACA8A5A4-D15C-4F9D-91F0-EE92FDF2E360}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
   <autoFilter ref="D212:E224" xr:uid="{97796C3A-D95E-4077-AA20-A8FE4145DAAD}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{622EF0B5-08C2-435D-AD90-194AA40AF483}" name="Month">
+    <tableColumn id="1" xr3:uid="{41D3FE7E-0B2A-4037-A526-EFC1F2E08083}" name="Month">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{1B155342-2AE7-4ACF-A9BA-20CE30CBC6E1}" name="Season" dataDxfId="28" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{C860C210-84DC-4D57-B9B9-7A4B859E451A}" name="Season" dataDxfId="16" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7487,7 +7511,7 @@
 </file>
 
 <file path=xl/tables/table24.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="30" xr:uid="{187B9ADF-B9E3-4BCF-ABE8-F47F94E4CCD2}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="41" xr:uid="{69FE65F4-EB1D-4E84-BD6C-6FFEC855BAFA}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
   <autoFilter ref="D231:S250" xr:uid="{1D72DD9B-C8FA-48F4-9A11-20231FF87B5A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -7507,52 +7531,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{3E609039-97C4-4729-BC48-B95334FF569D}" name="Temperature zone">
+    <tableColumn id="1" xr3:uid="{8C376FFF-40AA-4DB8-A527-41705B60404F}" name="Temperature zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{E18B5A5E-83DE-4F01-B188-8A16EF097844}" name="MAT (ºC)" dataDxfId="27" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{1E7E6284-EBB4-451D-8D4C-832725D2B9C3}" name="MAT (ºC)" dataDxfId="15" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{D36388A3-2885-4653-8CA5-464AC2653131}" name="Anaerobic lagoon" dataDxfId="26" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{D0107B29-9381-4BAE-9EF3-8DD415DCC240}" name="Anaerobic lagoon" dataDxfId="14" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{9C1AA35B-D1B9-4F13-9AFE-E084527288D4}" name="Digester / covered lagoons" dataDxfId="25" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{0CF5FFB0-89F9-4D73-A106-1F206160DD8D}" name="Digester / covered lagoons" dataDxfId="13" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{36AFD6DE-B5F7-4FA0-8661-5137CBBDF314}" name="Liquid systems" dataDxfId="24" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{FFBEF878-F5C8-4B9F-9DA1-83090B244944}" name="Liquid systems" dataDxfId="12" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{5C9AC720-CEA6-4B40-B794-DA1221D8A639}" name="Daily spread" dataDxfId="23" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{E88FABD7-C65C-4D77-AAEF-C1FF34A52E70}" name="Daily spread" dataDxfId="11" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{454AD809-4295-4C51-9928-79A9335C5131}" name="Composting (passive windrow)" dataDxfId="22" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{E4D0DC47-82D3-4078-A5F4-E10D80F4BB09}" name="Composting (passive windrow)" dataDxfId="10" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{3B58D073-0610-4780-89E8-72FD5F9DE29F}" name="Solid storage" dataDxfId="21" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{84369F6D-BF8F-4B6F-A75F-0BB8AD87CE06}" name="Solid storage" dataDxfId="9" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{4054B9BB-77F9-4163-856D-1F02090BD29E}" name="Pit storage" dataDxfId="20" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{9CBC2428-99EF-43CB-96A1-6CFAE74657FD}" name="Pit storage" dataDxfId="8" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{7761C4A1-7DEB-4A74-ABFE-16C4A40CA65E}" name="Deep litter" dataDxfId="19" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{6C2A76DE-94DE-462A-91E6-585911BDFDF6}" name="Deep litter" dataDxfId="7" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{8CBEF1D1-4341-4566-AE85-0BAE80513B23}" name="Poultry manure with bedding" dataDxfId="18" dataCellStyle="Content normal">
+    <tableColumn id="11" xr3:uid="{D7A8C618-0887-4C9A-B7CE-17EF1815BC38}" name="Poultry manure with bedding" dataDxfId="6" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{8AC3B56F-0E3B-46E4-881E-4A4C23336DB8}" name="Poultry manure without bedding" dataDxfId="17" dataCellStyle="Content normal">
+    <tableColumn id="12" xr3:uid="{1BD1076A-5D5F-4F9C-8C93-E31281C4BA05}" name="Poultry manure without bedding" dataDxfId="5" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{5E2D555B-CCCB-47A0-ABC6-4BBE59B69EB8}" name="Direct processing" dataDxfId="16" dataCellStyle="Content normal">
+    <tableColumn id="13" xr3:uid="{D7FB918E-84A7-4B01-BA09-6A6C6638801B}" name="Direct processing" dataDxfId="4" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{1ABF9296-D829-4357-B8D0-BF198B1CB558}" name="Direct application" dataDxfId="15" dataCellStyle="Content normal">
+    <tableColumn id="14" xr3:uid="{776C80DD-D7F4-47C0-9C8F-BA0150743FE8}" name="Direct application" dataDxfId="3" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{143C946F-C17F-411D-99BA-FB5337573E30}" name="Pasture range and paddock" dataDxfId="14" dataCellStyle="Content normal">
+    <tableColumn id="15" xr3:uid="{74216056-ABCD-44ED-9908-EFC45C6195BC}" name="Pasture range and paddock" dataDxfId="2" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{6876FAEC-5772-4EAC-8F56-60AF713901CD}" name="MAT raw" dataDxfId="13" dataCellStyle="Content normal">
+    <tableColumn id="16" xr3:uid="{72CED5A5-B876-4EE2-96C8-518AB55ADE87}" name="MAT raw" dataDxfId="1" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7561,16 +7585,16 @@
 </file>
 
 <file path=xl/tables/table25.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{462A48A5-6B2F-4D2D-8025-572DAB9FE02B}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="42" xr:uid="{8E5F8F0B-F913-4DED-8255-4ADAA75FD13D}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
   <autoFilter ref="D257:E259" xr:uid="{56E01C14-1BB8-4015-9158-4CEB4D3B605C}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{9C964A67-F781-4D99-8B91-5BFC8B5214FC}" name="Climate Zone">
+    <tableColumn id="1" xr3:uid="{3AAE867B-DCF1-4C39-8857-BFEF63EF6146}" name="Climate Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{EC008960-0F7E-4D6F-90B0-1B33D47696C5}" name="EFNi &amp; EFN2Oi" dataDxfId="12" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{F37BF008-7DFA-40AA-984E-28E069D52595}" name="EFNi &amp; EFN2Oi" dataDxfId="0" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7679,20 +7703,20 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1C2292D7-9159-4DA8-868F-97A60010C689}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{4CF8C6CB-2C3C-4BF2-8E14-B07A64D29D6B}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
   <autoFilter ref="D6:F14" xr:uid="{E0906749-7FC7-47DE-82F6-F796C4463018}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{556CCF88-C654-4845-97D7-9D7D362BCE69}" name="State/Territory">
+    <tableColumn id="1" xr3:uid="{E05ECB51-D48F-4298-A4DC-86B2EACBC145}" name="State/Territory">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{281E9821-9727-41EE-9BB2-A0EE34626517}" name="Common Name">
+    <tableColumn id="2" xr3:uid="{B98AC984-6A4D-4A60-873C-3C08B447A039}" name="Common Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{DB9ED2A9-4530-4389-9F51-62F4D51CBA86}" name="Abbreviation">
+    <tableColumn id="3" xr3:uid="{BAE1AE15-518D-46D1-A7AD-0726937B0A66}" name="Abbreviation">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -10542,62 +10566,62 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F86">
-    <cfRule type="cellIs" dxfId="11" priority="62" operator="lessThan">
+    <cfRule type="cellIs" dxfId="47" priority="62" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F128:F129">
-    <cfRule type="cellIs" dxfId="10" priority="21" operator="lessThan">
+    <cfRule type="cellIs" dxfId="46" priority="21" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F140:F141">
-    <cfRule type="cellIs" dxfId="9" priority="20" operator="lessThan">
+    <cfRule type="cellIs" dxfId="45" priority="20" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F152:F153">
-    <cfRule type="cellIs" dxfId="8" priority="19" operator="lessThan">
+    <cfRule type="cellIs" dxfId="44" priority="19" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F164:F165">
-    <cfRule type="cellIs" dxfId="7" priority="18" operator="lessThan">
+    <cfRule type="cellIs" dxfId="43" priority="18" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F252:F253">
-    <cfRule type="cellIs" dxfId="6" priority="93" operator="lessThan">
+    <cfRule type="cellIs" dxfId="42" priority="93" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F257:F258">
-    <cfRule type="cellIs" dxfId="5" priority="92" operator="lessThan">
+    <cfRule type="cellIs" dxfId="41" priority="92" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F262:F263">
-    <cfRule type="cellIs" dxfId="4" priority="91" operator="lessThan">
+    <cfRule type="cellIs" dxfId="40" priority="91" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F286:F287">
-    <cfRule type="cellIs" dxfId="3" priority="85" operator="lessThan">
+    <cfRule type="cellIs" dxfId="39" priority="85" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F291:F292">
-    <cfRule type="cellIs" dxfId="2" priority="84" operator="lessThan">
+    <cfRule type="cellIs" dxfId="38" priority="84" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F296:F297">
-    <cfRule type="cellIs" dxfId="1" priority="83" operator="lessThan">
+    <cfRule type="cellIs" dxfId="37" priority="83" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J211 E212:I212">
-    <cfRule type="cellIs" dxfId="0" priority="79" operator="lessThan">
+    <cfRule type="cellIs" dxfId="36" priority="79" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12805,7 +12829,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACE7628F-C552-4DBE-BEDA-1D3AB479C827}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74C8F99E-D558-4CFE-809C-6E2A65A32A40}">
   <dimension ref="A1:BY259"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -16797,15 +16821,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -17000,7 +17015,20 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACkAKgAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADIAKQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAHQAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAC8AdABcAHUAMAAwADMAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAdQAwADAAMgA3AFwAIgAgAFwAdQAwADAAMgA2ACAAcwBoACAAXAB1ADAAMAAyADYAIABcACIAXAB1ADAAMAAyADcAIQBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFUATgBEACgAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIAAwACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAE0ATQBTACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAaQB0AGwAZQBDAGUAbABsACwAIABTAG8AdQByAGMAZQBDAGUAbABsACwAXABuACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAEwARQBGAFQAKABTAG8AdQByAGMAZQBDAGUAbABsACwAIABGAEkATgBEACgAXAAiACwAXAAiACwAIABTAG8AdQByAGMAZQBDAGUAbABsACkAIAAtADEAKQAsACAAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFwAIgAsACAAXAAiAFwAIgApACAAXAB1ADAAMAAyADYAIABcACIAIABcACIAIABcAHUAMAAwADIANgAgAFQAaQB0AGwAZQBDAGUAbABsAFwAbgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBTAGMAYQBsAGkAbgBnACAAZgBhAGMAdABvAHIAIABiAGEAcwBlAGQAIABvAG4AIAB0AGgAZQAgAHcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAZQBtAHAAbABvAHkAZQBkACAAZAB1AHIAaQBuAGcAIAB0AGgAZQAgAGcAcgBvAHcAaQBuAGcAIABzAGUAYQBzAG8AbgAgAGMAdQBsAHQAaQB2AGEAdABpAG8AbgAgAHAAZQByAGkAbwBkAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBTAEYAdwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADMALgAxAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAdAB5AHAAZQBcACIALAAgAFwAIgBXAGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAHMAdQBiACAALQAgAHQAeQBwAGUAXAAiACwAIABcACIAUwBGAHcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFUAcABsAGEAbgBkAFwAIgAsACAAXAAiAFAAYQBkAGQAeQAgAHIAbwB0AGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVQBwAGwAYQBuAGQAXAAiACwAIABcACIARgBhAGwAbABvAHcAIAB3AGkAdABoAG8AdQB0ACAAZgBsAG8AbwBkAGkAbgBnACAAaQBuACAAcAByAGUAdgBpAG8AdQBzACAAeQBlAGEAcgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQwBvAG4AdABpAG4AdQBvAHUAcwBsAHkAIABmAGwAbwBvAGQAZQBkAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAgAHAAZQByAGkAbwBkAFwAIgAsACAAMAAuADcAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBNAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUAIABwAGUAcgBpAG8AZABzAFwAIgAsACAAMAAuADUANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAZQBkACAAYQBuAGQAIABkAGUAZQBwACAAdwBhAHQAZQByAFwAIgAsACAAXAAiAFIAZQBnAHUAbABhAHIAIAByAGEAaQBuAGYAZQBkAFwAIgAsACAAMAAuADUANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAZQBkACAAYQBuAGQAIABkAGUAZQBwACAAdwBhAHQAZQByAFwAIgAsACAAXAAiAEQAcgBvAHUAZwBoAHQAIABwAHIAbwBuAGUAXAAiACwAIAAwAC4AMQA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAYQBpAG4AZgBlAGQAIABhAG4AZAAgAGQAZQBlAHAAIAB3AGEAdABlAHIAXAAiACwAIABcACIARABlAGUAcAAgAHcAYQB0AGUAcgBcACIALAAgADAALgAwADYAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMAYwBhAGwAaQBuAGcAIABmAGEAYwB0AG8AcgAgAGIAYQBzAGUAZAAgAG8AbgAgAHQAaABlACAAdwBhAHQAZQByACAAcgBlAGcAaQBtAGUAIABlAG0AcABsAG8AeQBlAGQAIABpAG4AIAB0AGgAZQAgAHAAcgBlACAALQAgAHMAZQBhAHMAbwBuACAAYgBlAGYAbwByAGUAIAB0AGgAZQAgAGcAcgBvAHcAaQBuAGcAIABwAGUAcgBpAG8AZABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMARgBwAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBQAHIAZQBTAGUAYQBzAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAzAC4AMgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAcAByAGkAbwByACAAdABvACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuACAAcABlAHIAaQBvAGQAIABwAFwAIgAsACAAXAAiAFMARgBwAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAgAGYAbABvAG8AZABlAGQAIABwAHIAZQAtAHMAZQBhAHMAbwBuACAAXAB1ADAAMAAzAGMAMQA4ADAAIABkAGEAeQBzAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAgAGYAbABvAG8AZABlAGQAIABwAHIAZQAtAHMAZQBhAHMAbwBuACAAXAB1ADAAMAAzAGUAMQA4ADAAIABkAGEAeQBzAFwAIgAsACAAMAAuADgAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGwAbwBvAGQAZQBkACAAcAByAGUALQBzAGUAYQBzAG8AbgAgAFwAdQAwADAAMwBlADMAMAAgAGQAYQB5AHMAXAAiACwAIAAyAC4ANAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AZgBsAG8AbwBkAGUAZAAgAHAAcgBlAC0AcwBlAGEAcwBvAG4AIABcAHUAMAAwADMAZQAzADYANQAgAGQAYQB5AHMAXAAiACwAIAAwAC4ANQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAIABpAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMARgBPAEEAaQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAzAC4AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAGMAbAB1AGQAZQBkACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBzACAAYQBtAGUAbgBkAG0AZQBuAHQAIABhAHMAIABwAGUAcgAgAFYARQBFAFIARwAgAGUAcQB1AGEAdABpAG8AbgAgAGQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGgAZQByAGUAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABpAHMAIABhAHAAcABsAGkAZQBkACAAdABvACAAdABoAGUAIAByAGkAYwBlACAAZgBpAGUAbABkAHMAIAByAGEAdABoAGUAcgAgAHQAaABhAG4AIABvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAcwAsACAAUwBGAF8AbwAgAGkAcwAgAHMAZQB0ACAAdABvACAAMQAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADcALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdAAgAGkAXAAiACwAIABcACIAQwBGAE8AQQBpAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAcgBhAHcAIABpAG4AYwBvAHIAcABvAHIAYQB0AGUAZAAgAHMAaABvAHIAdABsAHkAIAAoAFwAdQAwADAAMwBjADMAMAAgAGQAYQB5AHMAKQAgAGIAZQBmAG8AcgBlACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAIgAsACAAMQAuADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAcgBhAHcAIABpAG4AYwBvAHIAcABvAHIAYQB0AGUAZAAgAGwAbwBuAGcAIAAoAFwAdQAwADAAMwBlADMAMAAgAGQAYQB5AHMAKQAgAGIAZQBmAG8AcgBlACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAIgAsACAAMAAuADEAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbQBwAG8AcwB0AFwAIgAsACAAMAAuADEANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGEAcgBtACAAeQBhAHIAZAAgAG0AYQBuAHUAcgBlAFwAIgAsACAAMAAuADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAHIAZQBlAG4AIABtAGEAbgB1AHIAZQBcACIALAAgADAALgA0ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEIAYQBzAGUAbABpAG4AZQBFAEYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQgBhAHMAZQBsAGkAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGMAbwBuAHQAaQBuAHUAbwB1AHMAbAB5ACAAZgBsAG8AbwBkAGUAZAAgAGYAaQBlAGwAZABzACAAdwBpAHQAaABvAHUAdAAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdABzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYAYwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAEMASAA0ACAALwAgAGgAYQAgAC8AIABkAGEAeQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA3AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAxAC4AMQA5ACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADcALgAxADoAIABSAGkAYwBlACAAQwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA3AC4AMQAuADEALgAxACAATQBlAHQAaABvAGQAIAAxACAALQAgAFIAaQBjAGUAIABDAHUAbAB0AGkAdgBhAHQAaQBvAG4AIABDAEgANAAgAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBcAG4ATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHIAaQBjAGUAIABjAHUAbAB0AGkAdgBhAHQAaQBvAG4AXABuAEUAXwByAGkAYwBlAFwAbgB0ACAAQwBIADQAXABuAEUAXwB7AHIAaQBjAGUAfQA9AFwAXABzAHUAbQBfAHcAXABcAHMAdQBtAF8AcABcAFwAcwB1AG0AXwBvACgAQQBfAHsAcgBpAGMAZQAsAHcAcABvAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAcgBpAGMAZQAsAHcAcABvAH0AXABcAHQAaQBtAGUAcwAgAHQAXwB7AHIAaQBjAGUALAB3AHAAbwB9ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXABuAEEAXwByAGkAYwBlAHcAcABvACAAPQAgAGEAbgBuAHUAYQBsACAAYQByAGUAYQAgAG8AZgAgAHIAaQBjAGUAIABjAHUAbAB0AGkAdgBhAHQAaQBvAG4AIAB1AG4AZABlAHIAIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAHcALAAgAHAAcgBlAC0AcwBlAGEAcwBvAG4AIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAHAALAAgAGEAbgBkACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0ACAAYwBvAG4AZABpAHQAaQBvAG4AIABvACAAKABoAGEAKQBcAG4ARQBGAF8AcgBpAGMAZQB3AHAAbwAgAD0AIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcgBpAGMAZQAgAGMAdQBsAHQAaQB2AGEAdABpAG8AbgAgAHUAbgBkAGUAcgAgAGMAbwBuAGQAaQB0AGkAbwBuAHMAIAB3ACwAIABwACwAIABhAG4AZAAgAG8AIAAoAGsAZwAgAEMASAA0AC8AaABhAC8AZABhAHkAKQBcAG4AdABfAHIAaQBjAGUAdwBwAG8AIAA9ACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuACAAcABlAHIAaQBvAGQAIABmAG8AcgAgAHIAaQBjAGUAIAB1AG4AZABlAHIAIABjAG8AbgBkAGkAdABpAG8AbgBzACAAdwAsACAAcAAsACAAYQBuAGQAIABvACAAKABkAGEAeQBzACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAF8AcgBpAGMAZQB3AHAAbwAsACAARQBGAF8AcgBpAGMAZQB3AHAAbwAsACAAdABfAHIAaQBjAGUAdwBwAG8ALABcAG4AIAAgACAAIABTAFUATQAoAEEAXwByAGkAYwBlAHcAcABvACAAKgAgAEUARgBfAHIAaQBjAGUAdwBwAG8AIAAqACAAdABfAHIAaQBjAGUAdwBwAG8AKQAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHIAaQBjAGUAIABjAHUAbAB0AGkAdgBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwByAGkAYwBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMASAA0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADcALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsAcgBpAGMAZQB9AD0AXABcAHMAdQBtAF8AdwBcAFwAcwB1AG0AXwBwAFwAXABzAHUAbQBfAG8AKABBAF8AewByAGkAYwBlACwAdwBwAG8AfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewByAGkAYwBlACwAdwBwAG8AfQBcAFwAdABpAG0AZQBzACAAdABfAHsAcgBpAGMAZQAsAHcAcABvAH0AKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAF8AcgBpAGMAZQB3AHAAbwBcACIALAAgAFwAIgBhAG4AbgB1AGEAbAAgAGEAcgBlAGEAIABvAGYAIAByAGkAYwBlACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuACAAdQBuAGQAZQByACAAdwBhAHQAZQByACAAcgBlAGcAaQBtAGUAIAB3ACwAIABwAHIAZQAtAHMAZQBhAHMAbwBuACAAdwBhAHQAZQByACAAcgBlAGcAaQBtAGUAIABwACwAIABhAG4AZAAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdAAgAGMAbwBuAGQAaQB0AGkAbwBuACAAbwBcACIALAAgAFwAIgBoAGEAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwByAGkAYwBlAHcAcABvAFwAIgAsACAAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAByAGkAYwBlACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuACAAdQBuAGQAZQByACAAYwBvAG4AZABpAHQAaQBvAG4AcwAgAHcALAAgAHAALAAgAGEAbgBkACAAbwBcACIALAAgAFwAIgBrAGcAIABDAEgANAAvAGgAYQAvAGQAYQB5AFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANwAuADEALgAxAC4AMQAsACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHQAXwByAGkAYwBlAHcAcABvAFwAIgAsACAAXAAiAGMAdQBsAHQAaQB2AGEAdABpAG8AbgAgAHAAZQByAGkAbwBkACAAZgBvAHIAIAByAGkAYwBlACAAdQBuAGQAZQByACAAYwBvAG4AZABpAHQAaQBvAG4AcwAgAHcALAAgAHAALAAgAGEAbgBkACAAbwBcACIALAAgAFwAIgBkAGEAeQBzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcwBcACIALAAgAFwAIgBuAHUAbQBiAGUAcgAgAG8AZgAgAGMAcgBvAHAAcABpAG4AZwAgAHMAZQBhAHMAbwBuAHMAIABpAG4AIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAbQBhAG4AYQBnAGUAZAAgAHQAaABpAHMAIAB3AGEAeQBcACIALAAgAFwAIgBzAGUAYQBzAG8AbgBzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAbgB1AG0AYgBlAHIAIABvAGYAIABzAGUAYQBzAG8AbgBzAFwAdQAwADAAMgA3ACAAdgBhAHIAaQBhAGIAbABlACAAYQBzACAAcABlAHIAIABWAEUARQBSAEcAIABkAGUAcwBjAHIAaQBwAHQAaQBvAG4AIABpAG4AIAA3AC4AMgAuADEAIABcAHUAMAAwADIANwBXAGgAZQByAGUAIAB0AGgAZQByAGUAIABpAHMAIABtAG8AcgBlACAAdABoAGEAbgAgAG8AbgBlACAAYwByAG8AcABwAGkAbgBnACAAcwBlAGEAcwBvAG4AIABwAGUAcgAgAHkAZQBhAHIALAAgAEEAcgBpAGMAZQAsAHcAcABvACAAcwBoAGEAbABsACAAYgBlACAAcwBjAGEAbABlAGQAIABhAGMAYwBvAHIAZABpAG4AZwBsAHkAXAB1ADAAMAAyADcAXAAiACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAbgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcgBpAGMAZQAgAGMAdQBsAHQAaQB2AGEAdABpAG8AbgBcAG4ARQBGAF8AcgBpAGMAZQB3AHAAbwBcAG4AawBnACAAQwBIADQALwBoAGEALwBkAGEAeQBcAG4ARQBGAF8AewByAGkAYwBlACwAdwBwAG8AfQA9AEUARgBfAGMAXABcAHQAaQBtAGUAcwAgAFMARgBfAHcAXABcAHQAaQBtAGUAcwAgAFMARgBfAHAAXABcAHQAaQBtAGUAcwAgAFMARgBfAG8AXABuAEUARgBfAGMAIAA9ACAAYgBhAHMAZQBsAGkAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGMAbwBuAHQAaQBuAHUAbwB1AHMAbAB5ACAAZgBsAG8AbwBkAGUAZAAgAGYAaQBlAGwAZABzACAAdwBpAHQAaABvAHUAdAAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdABzACAAKABrAGcAIABDAEgANAAvAGgAYQAvAGQAYQB5ACkAXABuAFMARgBfAHcAIAA9ACAAcwBjAGEAbABpAG4AZwAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAGQAdQByAGkAbgBnACAAdABoAGUAIABnAHIAbwB3AGkAbgBnACAAcwBlAGEAcwBvAG4AXABuAFMARgBfAHAAIAA9ACAAcwBjAGEAbABpAG4AZwAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAGkAbgAgAHQAaABlACAAcAByAGUALQBzAGUAYQBzAG8AbgBcAG4AUwBGAF8AbwAgAD0AIABzAGMAYQBsAGkAbgBnACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAeQBwAGUAIABhAG4AZAAgAGEAbQBvAHUAbgB0ACAAbwBmACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0AHMAIAAoAHMAZQB0ACAAdABvACAAMQAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdQBzAGUAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUARgBfAGMALAAgAFMARgBfAHcALAAgAFMARgBfAHAALAAgAFMARgBfAG8ALABcAG4AIAAgACAAIABFAEYAXwBjACAAKgAgAFMARgBfAHcAIAAqACAAUwBGAF8AcAAgACoAIABTAEYAXwBvAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHIAaQBjAGUAIABjAHUAbAB0AGkAdgBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUARgBfAHIAaQBjAGUAdwBwAG8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABDAEgANAAvAGgAYQAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADcALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAF8AewByAGkAYwBlACwAdwBwAG8AfQA9AEUARgBfAGMAXABcAHQAaQBtAGUAcwAgAFMARgBfAHcAXABcAHQAaQBtAGUAcwAgAFMARgBfAHAAXABcAHQAaQBtAGUAcwAgAFMARgBfAG8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADcALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AYwBcACIALAAgAFwAIgBiAGEAcwBlAGwAaQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAYwBvAG4AdABpAG4AdQBvAHUAcwBsAHkAIABmAGwAbwBvAGQAZQBkACAAZgBpAGUAbABkAHMAIAB3AGkAdABoAG8AdQB0ACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0AHMAXAAiACwAIABcACIAawBnACAAQwBIADQALwBoAGEALwBkAGEAeQBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgBfAHcAXAAiACwAIABcACIAcwBjAGEAbABpAG4AZwAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAGQAdQByAGkAbgBnACAAdABoAGUAIABnAHIAbwB3AGkAbgBnACAAcwBlAGEAcwBvAG4AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBGAF8AcABcACIALAAgAFwAIgBzAGMAYQBsAGkAbgBnACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAaQBuACAAdABoAGUAIABwAHIAZQAtAHMAZQBhAHMAbwBuAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgBfAG8AXAAiACwAIABcACIAcwBjAGEAbABpAG4AZwAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHkAcABlACAAYQBuAGQAIABhAG0AbwB1AG4AdAAgAG8AZgAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdABzAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADcALgAxAC4AMQAuADEALAAgACgAMwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgB3AFwAIgAsACAAXAAiAHcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAZAB1AHIAaQBuAGcAIABnAHIAbwB3AGkAbgBnACAAcwBlAGEAcwBvAG4AXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBwAFwAIgAsACAAXAAiAHAAcgBlAC0AcwBlAGEAcwBvAG4AIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAG8AXAAiACwAIABcACIAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0AFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXABuAE8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdABzACAAcwBjAGEAbABpAG4AZwAgAGYAYQBjAHQAbwByAFwAbgBTAEYAXwBvAFwAbgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAbgBTAEYAXwBvAD0AKAAxACsAXABcAHMAdQBtAF8AbwAoAFIATwBBAF8AbwBcAFwAdABpAG0AZQBzACAAQwBGAE8AQQBfAG8AKQApAF4AewAwAC4ANQA5AH0AXABuAFIATwBBAF8AbwAgAD0AIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAByAGEAdABlACAAbwBmACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0ACAAbwAgACgAdABvAG4AbgBlAHMALwBoAGEAKQBcAG4AQwBGAE8AQQBfAG8AIAA9ACAAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAbwBmACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0ACAAbwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUgBPAEEAXwBvACwAIABDAEYATwBBAF8AbwAsAFwAbgAgACAAIAAgACgAMQAgACsAIABTAFUATQAoAFIATwBBAF8AbwAgACoAIABDAEYATwBBAF8AbwApACkAIABeACAAMAAuADUAOQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABSAE8AQQBfAG8AMQAsACAAQwBGAE8AQQBfAG8AMQAsACAAUgBPAEEAXwBvADIALAAgAEMARgBPAEEAXwBvADIALAAgAFIATwBBAF8AbwAzACwAIABDAEYATwBBAF8AbwAzACwAIABSAE8AQQBfAG8ANAAsACAAQwBGAE8AQQBfAG8ANAAsACAAUgBPAEEAXwBvADUALAAgAEMARgBPAEEAXwBvADUALAAgAFIATwBBAF8AbwA2ACwAIABDAEYATwBBAF8AbwA2ACwAXABuACAAIAAgACAAKAAxACAAKwAgACgAKABSAE8AQQBfAG8AMQAgACoAIABDAEYATwBBAF8AbwAxACkAIAArACAAKABSAE8AQQBfAG8AMgAgACoAIABDAEYATwBBAF8AbwAyACkAIAArACAAKABSAE8AQQBfAG8AMwAgACoAIABDAEYATwBBAF8AbwAzACkAKwAgACgAUgBPAEEAXwBvADQAIAAqACAAQwBGAE8AQQBfAG8ANAApACAAKwAgACgAUgBPAEEAXwBvADUAIAAqACAAQwBGAE8AQQBfAG8ANQApACAAKwAgACgAUgBPAEEAXwBvADYAIAAqACAAQwBGAE8AQQBfAG8ANgApACkAKQAgAF4AIAAwAC4ANQA5AFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBPAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAcwAgAHMAYwBhAGwAaQBuAGcAIABmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBTAEYAXwBvAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANwAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAzACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAUwBGAF8AbwA9ACgAMQArAFwAXABzAHUAbQBfAG8AUgBPAEEAXwBvAFwAXAB0AGkAbQBlAHMAIABDAEYATwBBAF8AbwApAF4AewAwAC4ANQA5AH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMARgBfAG8APQAoADEAKwAgACgAKABSAE8AQQBfAG8AMQBcAFwAdABpAG0AZQBzACAAQwBGAE8AQQBfAG8AMQApACAAKwAgACgAUgBPAEEAXwBvADIAXABcAHQAaQBtAGUAcwAgAEMARgBPAEEAXwBvADIAKQAgACsAIAAoAFIATwBBAF8AbwAzAFwAXAB0AGkAbQBlAHMAIABDAEYATwBBAF8AbwAzACkAIAArACAAKABSAE8AQQBfAG8ANABcAFwAdABpAG0AZQBzACAAQwBGAE8AQQBfAG8ANAApACAAKwAgACgAUgBPAEEAXwBvADUAXABcAHQAaQBtAGUAcwAgAEMARgBPAEEAXwBvADUAKQAgACsAIAAoAFIATwBBAF8AbwA2AFwAXAB0AGkAbQBlAHMAIABDAEYATwBBAF8AbwA2ACkAKQBeAHsAMAAuADUAOQB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBPAEEAXwBvAFwAIgAsACAAXAAiAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHIAYQB0AGUAIABvAGYAIABvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAIABvAFwAIgAsACAAXAAiAHQAbwBuAG4AZQBzAC8AaABhAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBGAE8AQQBfAG8AXAAiACwAIABcACIAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAbwBmACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0ACAAbwBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBvAFwAIgAsACAAXAAiAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdAAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAGMAbAB1AGQAZQBkACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBzACAAYQBtAGUAbgBkAG0AZQBuAHQAIABhAHMAIABwAGUAcgAgAFYARQBFAFIARwAgAGUAcQB1AGEAdABpAG8AbgAgAGQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGgAZQByAGUAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABpAHMAIABhAHAAcABsAGkAZQBkACAAdABvACAAdABoAGUAIAByAGkAYwBlACAAZgBpAGUAbABkAHMAIAByAGEAdABoAGUAcgAgAHQAaABhAG4AIABvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAcwAsACAAUwBGAF8AbwAgAGkAcwAgAHMAZQB0ACAAdABvACAAMQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGUAYwBsAGEAcgBlAGQAIABlAGEAYwBoACAAYQBtAGUAbgBkAG0AZQBuAHQAIABzAGUAcABhAHIAYQB0AGUAbAB5ACAAdABvACAAYQBsAGwAbwB3ACAAcwB1AG0AbQBpAG4AZwAgAGkAbgAgAEUAeABjAGUAbAAgAGkAbgAgAG8AbgBlACAAZQBxAHUAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgAiAH0AXQAsACIAcAByAG8AagBlAGMAdABOAGEAbQBlAHMAIgA6AFsAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAEcAcgBvAHcAaQBuAGcAUwBlAGEAcwBvAG4AXwBVAG4AaQB0ACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAEcAcgBvAHcAaQBuAGcAUwBlAGEAcwBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAEQAYQB0AGEAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBUAGkAdABsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBVAG4AaQB0ACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBQAHIAZQBTAGUAYQBzAG8AbgBfAEQAYQB0AGEAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVABpAHQAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBVAG4AaQB0ACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFMAbwB1AHIAYwBlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAEQAYQB0AGEAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAFQAaQB0AGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEIAYQBzAGUAbABpAG4AZQBFAEYAXwBVAG4AaQB0ACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEIAYQBzAGUAbABpAG4AZQBFAEYAXwBTAG8AdQByAGMAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAEQAYQB0AGEAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBUAGkAdABsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AVQBuAGkAdAAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
@@ -17011,19 +17039,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACkAKgAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADIAKQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAHQAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAC8AdABcAHUAMAAwADMAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAdQAwADAAMgA3AFwAIgAgAFwAdQAwADAAMgA2ACAAcwBoACAAXAB1ADAAMAAyADYAIABcACIAXAB1ADAAMAAyADcAIQBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgAFwAdQAwADAAMgA2ACAAXAAiACAAXAAiACAAXAB1ADAAMAAyADYAIABUAGkAdABsAGUAQwBlAGwAbABcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAEcAcgBvAHcAaQBuAGcAUwBlAGEAcwBvAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAUwBjAGEAbABpAG4AZwAgAGYAYQBjAHQAbwByACAAYgBhAHMAZQBkACAAbwBuACAAdABoAGUAIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAGUAbQBwAGwAbwB5AGUAZAAgAGQAdQByAGkAbgBnACAAdABoAGUAIABnAHIAbwB3AGkAbgBnACAAcwBlAGEAcwBvAG4AIABjAHUAbAB0AGkAdgBhAHQAaQBvAG4AIABwAGUAcgBpAG8AZABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAUwBGAHcAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAEcAcgBvAHcAaQBuAGcAUwBlAGEAcwBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAEcAcgBvAHcAaQBuAGcAUwBlAGEAcwBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAzAC4AMQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAzACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAHQAeQBwAGUAXAAiACwAIABcACIAVwBhAHQAZQByACAAcgBlAGcAaQBtAGUAIABzAHUAYgAgAC0AIAB0AHkAcABlAFwAIgAsACAAXAAiAFMARgB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBVAHAAbABhAG4AZABcACIALAAgAFwAIgBQAGEAZABkAHkAIAByAG8AdABhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFUAcABsAGEAbgBkAFwAIgAsACAAXAAiAEYAYQBsAGwAbwB3ACAAdwBpAHQAaABvAHUAdAAgAGYAbABvAG8AZABpAG4AZwAgAGkAbgAgAHAAcgBlAHYAaQBvAHUAcwAgAHkAZQBhAHIAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEMAbwBuAHQAaQBuAHUAbwB1AHMAbAB5ACAAZgBsAG8AbwBkAGUAZABcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAUwBpAG4AZwBsAGUAIABkAHIAYQBpAG4AYQBnAGUAIABwAGUAcgBpAG8AZABcACIALAAgADAALgA3ADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACAAcABlAHIAaQBvAGQAcwBcACIALAAgADAALgA1ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGUAZAAgAGEAbgBkACAAZABlAGUAcAAgAHcAYQB0AGUAcgBcACIALAAgAFwAIgBSAGUAZwB1AGwAYQByACAAcgBhAGkAbgBmAGUAZABcACIALAAgADAALgA1ADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGUAZAAgAGEAbgBkACAAZABlAGUAcAAgAHcAYQB0AGUAcgBcACIALAAgAFwAIgBEAHIAbwB1AGcAaAB0ACAAcAByAG8AbgBlAFwAIgAsACAAMAAuADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAZQBkACAAYQBuAGQAIABkAGUAZQBwACAAdwBhAHQAZQByAFwAIgAsACAAXAAiAEQAZQBlAHAAIAB3AGEAdABlAHIAXAAiACwAIAAwAC4AMAA2AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBTAGMAYQBsAGkAbgBnACAAZgBhAGMAdABvAHIAIABiAGEAcwBlAGQAIABvAG4AIAB0AGgAZQAgAHcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAZQBtAHAAbABvAHkAZQBkACAAaQBuACAAdABoAGUAIABwAHIAZQAgAC0AIABzAGUAYQBzAG8AbgAgAGIAZQBmAG8AcgBlACAAdABoAGUAIABnAHIAbwB3AGkAbgBnACAAcABlAHIAaQBvAGQAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBTAEYAcABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMwAuADIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBQAHIAZQBTAGUAYQBzAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAHAAcgBpAG8AcgAgAHQAbwAgAGMAdQBsAHQAaQB2AGEAdABpAG8AbgAgAHAAZQByAGkAbwBkACAAcABcACIALAAgAFwAIgBTAEYAcABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4AIABmAGwAbwBvAGQAZQBkACAAcAByAGUALQBzAGUAYQBzAG8AbgAgAFwAdQAwADAAMwBjADEAOAAwACAAZABhAHkAcwBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4AIABmAGwAbwBvAGQAZQBkACAAcAByAGUALQBzAGUAYQBzAG8AbgAgAFwAdQAwADAAMwBlADEAOAAwACAAZABhAHkAcwBcACIALAAgADAALgA4ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBsAG8AbwBkAGUAZAAgAHAAcgBlAC0AcwBlAGEAcwBvAG4AIABcAHUAMAAwADMAZQAzADAAIABkAGEAeQBzAFwAIgAsACAAMgAuADQAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGYAbABvAG8AZABlAGQAIABwAHIAZQAtAHMAZQBhAHMAbwBuACAAXAB1ADAAMAAzAGUAMwA2ADUAIABkAGEAeQBzAFwAIgAsACAAMAAuADUAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0ACAAaQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAEYATwBBAGkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMwAuADMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMQAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgBjAGwAdQBkAGUAZAAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcwAgAGEAbQBlAG4AZABtAGUAbgB0ACAAYQBzACAAcABlAHIAIABWAEUARQBSAEcAIABlAHEAdQBhAHQAaQBvAG4AIABkAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBoAGUAcgBlACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAaQBzACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHQAaABlACAAcgBpAGMAZQAgAGYAaQBlAGwAZABzACAAcgBhAHQAaABlAHIAIAB0AGgAYQBuACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0AHMALAAgAFMARgBfAG8AIABpAHMAIABzAGUAdAAgAHQAbwAgADEALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA3ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAIABpAFwAIgAsACAAXAAiAEMARgBPAEEAaQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AHIAYQB3ACAAaQBuAGMAbwByAHAAbwByAGEAdABlAGQAIABzAGgAbwByAHQAbAB5ACAAKABcAHUAMAAwADMAYwAzADAAIABkAGEAeQBzACkAIABiAGUAZgBvAHIAZQAgAGMAdQBsAHQAaQB2AGEAdABpAG8AbgBcACIALAAgADEALgAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AHIAYQB3ACAAaQBuAGMAbwByAHAAbwByAGEAdABlAGQAIABsAG8AbgBnACAAKABcAHUAMAAwADMAZQAzADAAIABkAGEAeQBzACkAIABiAGUAZgBvAHIAZQAgAGMAdQBsAHQAaQB2AGEAdABpAG8AbgBcACIALAAgADAALgAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG0AcABvAHMAdABcACIALAAgADAALgAxADcAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBhAHIAbQAgAHkAYQByAGQAIABtAGEAbgB1AHIAZQBcACIALAAgADAALgAyADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwByAGUAZQBuACAAbQBhAG4AdQByAGUAXAAiACwAIAAwAC4ANAA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEIAYQBzAGUAbABpAG4AZQBFAEYAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEIAYQBzAGUAbABpAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABjAG8AbgB0AGkAbgB1AG8AdQBzAGwAeQAgAGYAbABvAG8AZABlAGQAIABmAGkAZQBsAGQAcwAgAHcAaQB0AGgAbwB1AHQAIABvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAGMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEIAYQBzAGUAbABpAG4AZQBFAEYAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABDAEgANAAgAC8AIABoAGEAIAAvACAAZABhAHkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEIAYQBzAGUAbABpAG4AZQBFAEYAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANwAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMQAuADEAOQApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA3AC4AMQA6ACAAUgBpAGMAZQAgAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANwAuADEALgAxAC4AMQAgAE0AZQB0AGgAbwBkACAAMQAgAC0AIABSAGkAYwBlACAAQwB1AGwAdABpAHYAYQB0AGkAbwBuACAAQwBIADQAIABFAG0AaQBzAHMAaQBvAG4AcwBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXABuAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAByAGkAYwBlACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAbgBFAF8AcgBpAGMAZQBcAG4AdAAgAEMASAA0AFwAbgBFAF8AewByAGkAYwBlAH0APQBcAFwAcwB1AG0AXwB3AFwAXABzAHUAbQBfAHAAXABcAHMAdQBtAF8AbwAoAEEAXwB7AHIAaQBjAGUALAB3AHAAbwB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AHIAaQBjAGUALAB3AHAAbwB9AFwAXAB0AGkAbQBlAHMAIAB0AF8AewByAGkAYwBlACwAdwBwAG8AfQApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBBAF8AcgBpAGMAZQB3AHAAbwAgAD0AIABhAG4AbgB1AGEAbAAgAGEAcgBlAGEAIABvAGYAIAByAGkAYwBlACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuACAAdQBuAGQAZQByACAAdwBhAHQAZQByACAAcgBlAGcAaQBtAGUAIAB3ACwAIABwAHIAZQAtAHMAZQBhAHMAbwBuACAAdwBhAHQAZQByACAAcgBlAGcAaQBtAGUAIABwACwAIABhAG4AZAAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdAAgAGMAbwBuAGQAaQB0AGkAbwBuACAAbwAgACgAaABhACkAXABuAEUARgBfAHIAaQBjAGUAdwBwAG8AIAA9ACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHIAaQBjAGUAIABjAHUAbAB0AGkAdgBhAHQAaQBvAG4AIAB1AG4AZABlAHIAIABjAG8AbgBkAGkAdABpAG8AbgBzACAAdwAsACAAcAAsACAAYQBuAGQAIABvACAAKABrAGcAIABDAEgANAAvAGgAYQAvAGQAYQB5ACkAXABuAHQAXwByAGkAYwBlAHcAcABvACAAPQAgAGMAdQBsAHQAaQB2AGEAdABpAG8AbgAgAHAAZQByAGkAbwBkACAAZgBvAHIAIAByAGkAYwBlACAAdQBuAGQAZQByACAAYwBvAG4AZABpAHQAaQBvAG4AcwAgAHcALAAgAHAALAAgAGEAbgBkACAAbwAgACgAZABhAHkAcwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQBfAHIAaQBjAGUAdwBwAG8ALAAgAEUARgBfAHIAaQBjAGUAdwBwAG8ALAAgAHQAXwByAGkAYwBlAHcAcABvACwAXABuACAAIAAgACAAUwBVAE0AKABBAF8AcgBpAGMAZQB3AHAAbwAgACoAIABFAEYAXwByAGkAYwBlAHcAcABvACAAKgAgAHQAXwByAGkAYwBlAHcAcABvACkAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAByAGkAYwBlACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AcgBpAGMAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAEgANABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA3AC4AMQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AHIAaQBjAGUAfQA9AFwAXABzAHUAbQBfAHcAXABcAHMAdQBtAF8AcABcAFwAcwB1AG0AXwBvACgAQQBfAHsAcgBpAGMAZQAsAHcAcABvAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAcgBpAGMAZQAsAHcAcABvAH0AXABcAHQAaQBtAGUAcwAgAHQAXwB7AHIAaQBjAGUALAB3AHAAbwB9ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBfAHIAaQBjAGUAdwBwAG8AXAAiACwAIABcACIAYQBuAG4AdQBhAGwAIABhAHIAZQBhACAAbwBmACAAcgBpAGMAZQAgAGMAdQBsAHQAaQB2AGEAdABpAG8AbgAgAHUAbgBkAGUAcgAgAHcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAdwAsACAAcAByAGUALQBzAGUAYQBzAG8AbgAgAHcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAcAAsACAAYQBuAGQAIABvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAIABjAG8AbgBkAGkAdABpAG8AbgAgAG8AXAAiACwAIABcACIAaABhAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AcgBpAGMAZQB3AHAAbwBcACIALAAgAFwAIgBlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcgBpAGMAZQAgAGMAdQBsAHQAaQB2AGEAdABpAG8AbgAgAHUAbgBkAGUAcgAgAGMAbwBuAGQAaQB0AGkAbwBuAHMAIAB3ACwAIABwACwAIABhAG4AZAAgAG8AXAAiACwAIABcACIAawBnACAAQwBIADQALwBoAGEALwBkAGEAeQBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADcALgAxAC4AMQAuADEALAAgACgAMgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgB0AF8AcgBpAGMAZQB3AHAAbwBcACIALAAgAFwAIgBjAHUAbAB0AGkAdgBhAHQAaQBvAG4AIABwAGUAcgBpAG8AZAAgAGYAbwByACAAcgBpAGMAZQAgAHUAbgBkAGUAcgAgAGMAbwBuAGQAaQB0AGkAbwBuAHMAIAB3ACwAIABwACwAIABhAG4AZAAgAG8AXAAiACwAIABcACIAZABhAHkAcwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHMAXAAiACwAIABcACIAbgB1AG0AYgBlAHIAIABvAGYAIABjAHIAbwBwAHAAaQBuAGcAIABzAGUAYQBzAG8AbgBzACAAaQBuACAAcgBlAHAAbwByAHQAaQBuAGcAIABwAGUAcgBpAG8AZAAgAG0AYQBuAGEAZwBlAGQAIAB0AGgAaQBzACAAdwBhAHkAXAAiACwAIABcACIAcwBlAGEAcwBvAG4AcwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AG4AdQBtAGIAZQByACAAbwBmACAAcwBlAGEAcwBvAG4AcwBcAHUAMAAwADIANwAgAHYAYQByAGkAYQBiAGwAZQAgAGEAcwAgAHAAZQByACAAVgBFAEUAUgBHACAAZABlAHMAYwByAGkAcAB0AGkAbwBuACAAaQBuACAANwAuADIALgAxACAAXAB1ADAAMAAyADcAVwBoAGUAcgBlACAAdABoAGUAcgBlACAAaQBzACAAbQBvAHIAZQAgAHQAaABhAG4AIABvAG4AZQAgAGMAcgBvAHAAcABpAG4AZwAgAHMAZQBhAHMAbwBuACAAcABlAHIAIAB5AGUAYQByACwAIABBAHIAaQBjAGUALAB3AHAAbwAgAHMAaABhAGwAbAAgAGIAZQAgAHMAYwBhAGwAZQBkACAAYQBjAGMAbwByAGQAaQBuAGcAbAB5AFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHIAaQBjAGUAIABjAHUAbAB0AGkAdgBhAHQAaQBvAG4AXABuAEUARgBfAHIAaQBjAGUAdwBwAG8AXABuAGsAZwAgAEMASAA0AC8AaABhAC8AZABhAHkAXABuAEUARgBfAHsAcgBpAGMAZQAsAHcAcABvAH0APQBFAEYAXwBjAFwAXAB0AGkAbQBlAHMAIABTAEYAXwB3AFwAXAB0AGkAbQBlAHMAIABTAEYAXwBwAFwAXAB0AGkAbQBlAHMAIABTAEYAXwBvAFwAbgBFAEYAXwBjACAAPQAgAGIAYQBzAGUAbABpAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABjAG8AbgB0AGkAbgB1AG8AdQBzAGwAeQAgAGYAbABvAG8AZABlAGQAIABmAGkAZQBsAGQAcwAgAHcAaQB0AGgAbwB1AHQAIABvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAcwAgACgAawBnACAAQwBIADQALwBoAGEALwBkAGEAeQApAFwAbgBTAEYAXwB3ACAAPQAgAHMAYwBhAGwAaQBuAGcAIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdwBhAHQAZQByACAAcgBlAGcAaQBtAGUAIABkAHUAcgBpAG4AZwAgAHQAaABlACAAZwByAG8AdwBpAG4AZwAgAHMAZQBhAHMAbwBuAFwAbgBTAEYAXwBwACAAPQAgAHMAYwBhAGwAaQBuAGcAIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdwBhAHQAZQByACAAcgBlAGcAaQBtAGUAIABpAG4AIAB0AGgAZQAgAHAAcgBlAC0AcwBlAGEAcwBvAG4AXABuAFMARgBfAG8AIAA9ACAAcwBjAGEAbABpAG4AZwAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHkAcABlACAAYQBuAGQAIABhAG0AbwB1AG4AdAAgAG8AZgAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdABzACAAKABzAGUAdAAgAHQAbwAgADEAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHUAcwBlACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAEYAXwBjACwAIABTAEYAXwB3ACwAIABTAEYAXwBwACwAIABTAEYAXwBvACwAXABuACAAIAAgACAARQBGAF8AYwAgACoAIABTAEYAXwB3ACAAKgAgAFMARgBfAHAAIAAqACAAUwBGAF8AbwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAByAGkAYwBlACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYAXwByAGkAYwBlAHcAcABvAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAAQwBIADQALwBoAGEALwBkAGEAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA3AC4AMQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADIAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUARgBfAHsAcgBpAGMAZQAsAHcAcABvAH0APQBFAEYAXwBjAFwAXAB0AGkAbQBlAHMAIABTAEYAXwB3AFwAXAB0AGkAbQBlAHMAIABTAEYAXwBwAFwAXAB0AGkAbQBlAHMAIABTAEYAXwBvAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA3ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAGMAXAAiACwAIABcACIAYgBhAHMAZQBsAGkAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGMAbwBuAHQAaQBuAHUAbwB1AHMAbAB5ACAAZgBsAG8AbwBkAGUAZAAgAGYAaQBlAGwAZABzACAAdwBpAHQAaABvAHUAdAAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdABzAFwAIgAsACAAXAAiAGsAZwAgAEMASAA0AC8AaABhAC8AZABhAHkAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEYAXwB3AFwAIgAsACAAXAAiAHMAYwBhAGwAaQBuAGcAIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdwBhAHQAZQByACAAcgBlAGcAaQBtAGUAIABkAHUAcgBpAG4AZwAgAHQAaABlACAAZwByAG8AdwBpAG4AZwAgAHMAZQBhAHMAbwBuAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgBfAHAAXAAiACwAIABcACIAcwBjAGEAbABpAG4AZwAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAGkAbgAgAHQAaABlACAAcAByAGUALQBzAGUAYQBzAG8AbgBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEYAXwBvAFwAIgAsACAAXAAiAHMAYwBhAGwAaQBuAGcAIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdAB5AHAAZQAgAGEAbgBkACAAYQBtAG8AdQBuAHQAIABvAGYAIABvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAcwBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA3AC4AMQAuADEALgAxACwAIAAoADMAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAdwBcACIALAAgAFwAIgB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAGQAdQByAGkAbgBnACAAZwByAG8AdwBpAG4AZwAgAHMAZQBhAHMAbwBuAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcABcACIALAAgAFwAIgBwAHIAZQAtAHMAZQBhAHMAbwBuACAAdwBhAHQAZQByACAAcgBlAGcAaQBtAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBvAFwAIgAsACAAXAAiAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdABcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFwAbgBPAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAcwAgAHMAYwBhAGwAaQBuAGcAIABmAGEAYwB0AG8AcgBcAG4AUwBGAF8AbwBcAG4AZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcAG4AUwBGAF8AbwA9ACgAMQArAFwAXABzAHUAbQBfAG8AKABSAE8AQQBfAG8AXABcAHQAaQBtAGUAcwAgAEMARgBPAEEAXwBvACkAKQBeAHsAMAAuADUAOQB9AFwAbgBSAE8AQQBfAG8AIAA9ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAcgBhAHQAZQAgAG8AZgAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdAAgAG8AIAAoAHQAbwBuAG4AZQBzAC8AaABhACkAXABuAEMARgBPAEEAXwBvACAAPQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAG8AZgAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdAAgAG8AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFIATwBBAF8AbwAsACAAQwBGAE8AQQBfAG8ALABcAG4AIAAgACAAIAAoADEAIAArACAAUwBVAE0AKABSAE8AQQBfAG8AIAAqACAAQwBGAE8AQQBfAG8AKQApACAAXgAgADAALgA1ADkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUgBPAEEAXwBvADEALAAgAEMARgBPAEEAXwBvADEALAAgAFIATwBBAF8AbwAyACwAIABDAEYATwBBAF8AbwAyACwAIABSAE8AQQBfAG8AMwAsACAAQwBGAE8AQQBfAG8AMwAsACAAUgBPAEEAXwBvADQALAAgAEMARgBPAEEAXwBvADQALAAgAFIATwBBAF8AbwA1ACwAIABDAEYATwBBAF8AbwA1ACwAIABSAE8AQQBfAG8ANgAsACAAQwBGAE8AQQBfAG8ANgAsAFwAbgAgACAAIAAgACgAMQAgACsAIAAoACgAUgBPAEEAXwBvADEAIAAqACAAQwBGAE8AQQBfAG8AMQApACAAKwAgACgAUgBPAEEAXwBvADIAIAAqACAAQwBGAE8AQQBfAG8AMgApACAAKwAgACgAUgBPAEEAXwBvADMAIAAqACAAQwBGAE8AQQBfAG8AMwApACsAIAAoAFIATwBBAF8AbwA0ACAAKgAgAEMARgBPAEEAXwBvADQAKQAgACsAIAAoAFIATwBBAF8AbwA1ACAAKgAgAEMARgBPAEEAXwBvADUAKQAgACsAIAAoAFIATwBBAF8AbwA2ACAAKgAgAEMARgBPAEEAXwBvADYAKQApACkAIABeACAAMAAuADUAOQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0AHMAIABzAGMAYQBsAGkAbgBnACAAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAUwBGAF8AbwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADcALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMwApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMARgBfAG8APQAoADEAKwBcAFwAcwB1AG0AXwBvAFIATwBBAF8AbwBcAFwAdABpAG0AZQBzACAAQwBGAE8AQQBfAG8AKQBeAHsAMAAuADUAOQB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBTAEYAXwBvAD0AKAAxACsAIAAoACgAUgBPAEEAXwBvADEAXABcAHQAaQBtAGUAcwAgAEMARgBPAEEAXwBvADEAKQAgACsAIAAoAFIATwBBAF8AbwAyAFwAXAB0AGkAbQBlAHMAIABDAEYATwBBAF8AbwAyACkAIAArACAAKABSAE8AQQBfAG8AMwBcAFwAdABpAG0AZQBzACAAQwBGAE8AQQBfAG8AMwApACAAKwAgACgAUgBPAEEAXwBvADQAXABcAHQAaQBtAGUAcwAgAEMARgBPAEEAXwBvADQAKQAgACsAIAAoAFIATwBBAF8AbwA1AFwAXAB0AGkAbQBlAHMAIABDAEYATwBBAF8AbwA1ACkAIAArACAAKABSAE8AQQBfAG8ANgBcAFwAdABpAG0AZQBzACAAQwBGAE8AQQBfAG8ANgApACkAXgB7ADAALgA1ADkAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIATwBBAF8AbwBcACIALAAgAFwAIgBhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAByAGEAdABlACAAbwBmACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0ACAAbwBcACIALAAgAFwAIgB0AG8AbgBuAGUAcwAvAGgAYQBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgBPAEEAXwBvAFwAIgAsACAAXAAiAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAG8AZgAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdAAgAG8AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAbwBcACIALAAgAFwAIgBvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAAMQAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgBjAGwAdQBkAGUAZAAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcwAgAGEAbQBlAG4AZABtAGUAbgB0ACAAYQBzACAAcABlAHIAIABWAEUARQBSAEcAIABlAHEAdQBhAHQAaQBvAG4AIABkAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBoAGUAcgBlACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAaQBzACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHQAaABlACAAcgBpAGMAZQAgAGYAaQBlAGwAZABzACAAcgBhAHQAaABlAHIAIAB0AGgAYQBuACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0AHMALAAgAFMARgBfAG8AIABpAHMAIABzAGUAdAAgAHQAbwAgADEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAbABhAHIAZQBkACAAZQBhAGMAaAAgAGEAbQBlAG4AZABtAGUAbgB0ACAAcwBlAHAAYQByAGEAdABlAGwAeQAgAHQAbwAgAGEAbABsAG8AdwAgAHMAdQBtAG0AaQBuAGcAIABpAG4AIABFAHgAYwBlAGwAIABpAG4AIABvAG4AZQAgAGUAcQB1AGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAEcAcgBvAHcAaQBuAGcAUwBlAGEAcwBvAG4AXwBUAGkAdABsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8AVQBuAGkAdAAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAEcAcgBvAHcAaQBuAGcAUwBlAGEAcwBvAG4AXwBEAGEAdABhACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAF8AVABpAHQAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAF8AVQBuAGkAdAAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBQAHIAZQBTAGUAYQBzAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBEAGEAdABhACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFQAaQB0AGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVQBuAGkAdAAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBTAG8AdQByAGMAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBEAGEAdABhACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEIAYQBzAGUAbABpAG4AZQBFAEYAXwBUAGkAdABsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAF8AVQBuAGkAdAAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEIAYQBzAGUAbABpAG4AZQBFAEYAXwBEAGEAdABhACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AVABpAHQAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAFUAbgBpAHQAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAFMAbwB1AHIAYwBlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQB0AGkAbwBuACIAXQAsACIAbABvAGMAYQBsAGUAIgA6AHsAIgBsAGkAcwB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAcgBvAHcAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBjAG8AbAB1AG0AbgBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUABvAHMAaQB0AGkAbwBuAHMAIgA6AFsAMwBdACwAIgBkAGUAYwBpAG0AYQBsAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiAC4AIgAsACIAZABhAHQAZQBPAHIAZABlAHIAIgA6ACIARABNAFkAIgAsACIAYwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsACIAOgAiACQAIgAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbABMAGUAYQBkACIAOgB0AHIAdQBlACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAZQBwAEIAeQBTAHAAYQBjAGUAIgA6AGYAYQBsAHMAZQAsACIAcgBvAHcATABlAHQAdABlAHIAIgA6ACIAUgAiACwAIgBjAG8AbAB1AG0AbgBMAGUAdAB0AGUAcgAiADoAIgBDACIALAAiAHIAYwBMAGUAZgB0AEIAcgBhAGMAawBlAHQAIgA6ACIAWwAiACwAIgByAGMAUgBpAGcAaAB0AEIAcgBhAGMAawBlAHQAIgA6ACIAXQAiACwAIgBzAHQAYQB0AGUAbQBlAG4AdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGwAbwBjAGEAbABlAE4AYQBtAGUAIgA6ACIAZQBuAC0AdQBzACIAfQB9AA==</AFEJSONBlob>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809E3D44-A88D-4EBF-A307-6B8CE77A3361}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -17042,7 +17058,23 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -17051,12 +17083,4 @@
     <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Excel/7_RiceCultivation_WIP_v02.prename.bak.xlsx
+++ b/Excel/7_RiceCultivation_WIP_v02.prename.bak.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF755126-83E1-4668-B5BA-B89C99D2F398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECF1F9C3-862D-4719-96D1-773CEF26C7BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="28800" windowHeight="15345" firstSheet="3" activeTab="7" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="1350" yWindow="360" windowWidth="36255" windowHeight="19140" firstSheet="3" activeTab="7" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -22,9 +22,6 @@
     <sheet name="Constants - Rice cultivation" sheetId="110" r:id="rId7"/>
     <sheet name="Constants - Common" sheetId="120" r:id="rId8"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId9"/>
-  </externalReferences>
   <definedNames>
     <definedName name="AgResidues_Equations_Leaching.VEERG_6_3_1_1__1__LeachingAndRunoffEmissionsCropAndPastureResidue">_xlfn.LAMBDA(_xlpm.Mleachcp,_xlpm.EFleach,_xlpm.CgN2O, _xlpm.Mleachcp * _xlpm.EFleach * _xlpm.CgN2O * 10 ^ (-3))</definedName>
     <definedName name="AgResidues_Equations_Leaching.VEERG_6_3_1_1__1__LeachingAndRunoffEmissionsCropAndPastureResidue_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(5, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Mleachcp","mass of nitrogen lost through leaching and runoff from the crop residue c or pasture residue p (kg N)";"EFleach","emission factor for leaching and runoff (kg N2O-N/kg N)";"CgN2O","factor to convert elemental mass of nitrous oxide to molecular mass (dimensionless)";"c","Crop residue type";"p","Pasture residue type"}, _xlpm.r, _xlpm.c))))</definedName>
@@ -56,7 +53,17 @@
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Title">_xlfn.LAMBDA("Convert nitrous oxide emissions to carbon dioxide equivalent emissions")</definedName>
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Unit">_xlfn.LAMBDA("t CO2e")</definedName>
     <definedName name="Common_Equations.Common_ConvertN2OToCO2e_Variable">_xlfn.LAMBDA("EN2O CO2e")</definedName>
-    <definedName name="Common_InputFunctions.Common_GetMCFTemperatureZone">_xlfn.LAMBDA(_xlpm.Temperature,_xlpm.MMS,_xlpm.TemperatureArray,_xlpm.MMSArray,_xlpm.ReturnArray, _xlfn.XLOOKUP(MEDIAN(_xlpm.Temperature, MIN(_xlpm.TemperatureArray), MAX(_xlpm.TemperatureArray)), _xlpm.TemperatureArray, _xlfn.XLOOKUP(_xlpm.MMS, _xlpm.MMSArray, _xlpm.ReturnArray)))</definedName>
+    <definedName name="Common_InputFunctions.Common_GetMCFTemperatureZone">_xlfn.LAMBDA(_xlpm.Temperature,_xlpm.MMS,_xlpm.TemperatureArray,_xlpm.MMSArray,_xlpm.ReturnArray,
+    _xlfn.XLOOKUP(
+        MEDIAN(
+            ROUND(_xlpm.Temperature, 0),
+            MIN(_xlpm.TemperatureArray),
+            MAX(_xlpm.TemperatureArray)
+        ),
+        _xlpm.TemperatureArray,
+        _xlfn.XLOOKUP(_xlpm.MMS, _xlpm.MMSArray, _xlpm.ReturnArray)
+    )
+)</definedName>
     <definedName name="Common_InputFunctions.CommonCropping_GetFracWET">_xlfn.LAMBDA(_xlpm.LeachingZone,_xlpm.ProductionSystem,_xlpm.LeachingZoneLookup,_xlpm.LeachingZoneFracWETLookup,_xlpm.ProductionSystemLookup,_xlpm.ProductionSystemFracWETLookup, _xlfn.LET(_xlpm.LeachingZoneFracWET, Common_InputFunctions.Utility_LookupValueInTableNumber(_xlpm.LeachingZone, _xlpm.LeachingZoneLookup, _xlpm.LeachingZoneFracWETLookup), _xlpm.ProductionSystemFracWET, Common_InputFunctions.Utility_LookupValueInTableNumber(_xlpm.ProductionSystem, _xlpm.ProductionSystemLookup, _xlpm.ProductionSystemFracWETLookup), IF(_xlpm.LeachingZoneFracWET + _xlpm.ProductionSystemFracWET &gt; 0, 1, 0)))</definedName>
     <definedName name="Common_InputFunctions.getOverlappingReportingCycles">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingCycleStart, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, MONTH(_xlpm.ReportingCycleStart), _xlpm.d, DAY(_xlpm.ReportingCycleStart), _xlpm.PeriodEnd, _xlfn.LAMBDA(_xlpm.st, EDATE(_xlpm.st, 12) - 1), _xlpm.A, _xlpm.S - 365, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (_xlpm.PeriodEnd(DATE(_xlpm.ya, _xlpm.m, _xlpm.d)) &lt; _xlpm.S), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1)))</definedName>
     <definedName name="Common_InputFunctions.getOverlappingReportingPeriods">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingCycleStart, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, MONTH(_xlpm.ReportingCycleStart), _xlpm.d, DAY(_xlpm.ReportingCycleStart), _xlpm.PeriodEnd, _xlfn.LAMBDA(_xlpm.st, EDATE(_xlpm.st, 12) - 1), _xlpm.A, _xlpm.S - 365, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (_xlpm.PeriodEnd(DATE(_xlpm.ya, _xlpm.m, _xlpm.d)) &lt; _xlpm.S), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), _xlpm.n, MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1), _xlpm.yrs, _xlfn.SEQUENCE(_xlpm.n, 1, _xlpm.firstYear, 1), _xlpm.starts, DATE(_xlpm.yrs, _xlpm.m, _xlpm.d), _xlpm.ends, _xlfn.MAP(_xlpm.starts, _xlpm.PeriodEnd), _xlpm.tag, IF(_xlpm.starts = _xlpm.ReportingCycleStart, " (This reporting cycle)", ""), _xlpm.startsText, TEXT(_xlpm.starts, "dd mmm yyyy"), _xlpm.endsText, TEXT(_xlpm.ends, "dd mmm yyyy"), IF(_xlpm.n = 0, "", _xlfn.HSTACK(_xlpm.startsText &amp; " to " &amp; _xlpm.endsText &amp; _xlpm.tag))))</definedName>
@@ -72,9 +79,28 @@
     <definedName name="Common_InputFunctions.Utility_LookupN2OEFFromProdIrrigationRainfall">_xlfn.LAMBDA(_xlpm.ProductionSystem,_xlpm.IrrigationMethod,_xlpm.RainfallZone,_xlpm.ProductionSystemArray,_xlpm.IrrigationMethodArray,_xlpm.RainfallZoneArray,_xlpm.ReturnArray, _xlfn.LET(_xlpm.IrrigationMethod, IF(_xlpm.IrrigationMethod = "Not irrigated", "Not irrigated", "Any"), _xlpm.RainfallZone, IF(_xlpm.IrrigationMethod = "Not irrigated", _xlpm.RainfallZone, "Any"), _xlfn.XLOOKUP(1, (_xlpm.ProductionSystemArray = _xlpm.ProductionSystem) * (_xlpm.IrrigationMethodArray = _xlpm.IrrigationMethod) * (_xlpm.RainfallZoneArray = _xlpm.RainfallZone), _xlpm.ReturnArray)))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupValueInTable">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.LookupArray,_xlpm.ReturnArray, _xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, ""))</definedName>
     <definedName name="Common_InputFunctions.Utility_LookupValueInTableNumber">_xlfn.LAMBDA(_xlpm.LookupValue,_xlpm.LookupArray,_xlpm.ReturnArray, IF(ISNUMBER(_xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, "")), _xlfn.XLOOKUP(_xlpm.LookupValue, _xlpm.LookupArray, _xlpm.ReturnArray, ""), 0))</definedName>
-    <definedName name="Common_InputFunctions.Utility_LookupValueInTableOneColumnAndHeader">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray, _xlfn.XLOOKUP(_xlpm.LookupValue1, _xlpm.LookupArray1, _xlfn.XLOOKUP(_xlpm.LookupValue2, _xlpm.LookupArray2, _xlpm.ReturnArray)))</definedName>
-    <definedName name="Common_InputFunctions.Utility_LookupValueInTableTwoColumns">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray, _xlfn.XLOOKUP(1, (_xlpm.LookupArray1 = _xlpm.LookupValue1) * (_xlpm.LookupArray2 = _xlpm.LookupValue2), _xlpm.ReturnArray, ""))</definedName>
+    <definedName name="Common_InputFunctions.Utility_LookupValueInTableOneColumnAndHeader">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray,_xlop.ValueIfFalse,
+    IFERROR(
+        _xlfn.XLOOKUP(_xlpm.LookupValue1, _xlpm.LookupArray1,
+            _xlfn.XLOOKUP(_xlpm.LookupValue2, _xlpm.LookupArray2, _xlpm.ReturnArray)
+        ),
+        IF(_xlfn.ISOMITTED(_xlpm.ValueIfFalse), "", _xlpm.ValueIfFalse)
+    )
+)</definedName>
+    <definedName name="Common_InputFunctions.Utility_LookupValueInTableTwoColumns">_xlfn.LAMBDA(_xlpm.LookupValue1,_xlpm.LookupValue2,_xlpm.LookupArray1,_xlpm.LookupArray2,_xlpm.ReturnArray,_xlop.ValueIFFalse,
+    _xlfn.XLOOKUP(1, (_xlpm.LookupArray1=_xlpm.LookupValue1)*(_xlpm.LookupArray2=_xlpm.LookupValue2), _xlpm.ReturnArray, IF(_xlfn.ISOMITTED(_xlpm.ValueIFFalse), "", _xlpm.ValueIFFalse))
+)</definedName>
+    <definedName name="Common_InputFunctions.Utility_ResultsItemFromEquationTitleAndSource">_xlfn.LAMBDA(_xlpm.TitleCell,_xlpm.SourceCell,
+    SUBSTITUTE(LEFT(_xlpm.SourceCell, FIND(",", _xlpm.SourceCell) -1), "VEERG 2026: ", "") &amp; " " &amp; _xlpm.TitleCell
+)</definedName>
     <definedName name="Common_InputFunctions.Utility_SourceHyperlink">_xlfn.LAMBDA(_xlpm.TargetCell, _xlfn.LET(_xlpm.sh, _xlfn.TEXTAFTER(CELL("filename", _xlpm.TargetCell), "]"), _xlpm.addr, CELL("address", _xlpm.TargetCell), "#'" &amp; _xlpm.sh &amp; "'!" &amp; _xlpm.addr))</definedName>
+    <definedName name="Common_InputFunctions.Utility_SourceHyperlinkDifferentSheet">_xlfn.LAMBDA(_xlpm.TargetCell,
+  _xlfn.LET(
+    _xlpm.sh, _xlfn.TEXTAFTER(CELL("filename", _xlpm.TargetCell), "]"),
+    _xlpm.addr, CELL("address", _xlpm.TargetCell),
+    "#" &amp; _xlpm.addr
+  )
+)</definedName>
     <definedName name="Common_InputFunctions.Utility_SplitStringIntoArray">_xlfn.LAMBDA(_xlpm.Cell,_xlpm.Delimiter,_xlop.CharacterToRemove1,_xlop.CharacterToRemove2, _xlfn.FILTERXML("&lt;t&gt;&lt;s&gt;" &amp; SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.Cell, _xlpm.CharacterToRemove1, ""), _xlpm.CharacterToRemove2, ""), _xlpm.Delimiter, "&lt;/s&gt;&lt;s&gt;") &amp; "&lt;/s&gt;&lt;/t&gt;", "//s"))</definedName>
     <definedName name="Common_InputFunctions.Utility_SumQuantityFromCriteria">_xlfn.LAMBDA(_xlpm.Criteria1,_xlpm.Criteria1TypeArray,_xlpm.Quantity,_xlop.Multiplier,_xlop.Criteria2,_xlop.Criteria2Array, _xlfn.LET(_xlpm.multiplier, IF(_xlfn.ISOMITTED(_xlpm.Multiplier), 1, _xlpm.Multiplier), _xlpm.quantity, _xlpm.Quantity * _xlpm.multiplier, _xlpm.criteria1, --(_xlpm.Criteria1TypeArray = _xlpm.Criteria1), _xlpm.criteria2, IF(_xlfn.ISOMITTED(_xlpm.Criteria2), 1, --(_xlpm.Criteria2Array = _xlpm.Criteria2)), SUMPRODUCT(_xlpm.criteria1 * _xlpm.criteria2 * _xlpm.quantity)))</definedName>
     <definedName name="Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(9, 3, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"State/Territory","Common Name","Abbreviation";"New South Wales","New South Wales","NSW";"Australian Capital Territory","ACT","ACT";"Victoria","Victoria","VIC";"Queensland","Queensland","QLD";"South Australia","South Australia","SA";"Western Australia","Western Australia","WA";"Tasmania","Tasmania","TAS";"Northern Territory","Northern Territory","NT"}, _xlpm.r, _xlpm.c))))</definedName>
@@ -285,7 +311,13 @@
     <definedName name="RiceCultivation_SourceData.SourceData_RiceCultivation_BaselineEF_Unit">_xlfn.LAMBDA("kg CH4 / ha / day")</definedName>
     <definedName name="RiceCultivation_SourceData.SourceData_RiceCultivation_BaselineEF_Variable">_xlfn.LAMBDA("EFc")</definedName>
     <definedName name="RiceCultivation_SourceData.SourceData_RiceCultivation_BaselineEF_Variation">_xlfn.LAMBDA("")</definedName>
-    <definedName name="RiceCultivation_SourceData.SourceData_RiceCultivation_OrganicAmendmentConversionFactor_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(7, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Organic amendment i","CFOAi";"Straw incorporated shortly (&lt;30 days) before cultivation",1;"Straw incorporated long (&gt;30 days) before cultivation",0.19;"Compost",0.17;"Farm yard manure",0.21;"Green manure",0.45;"Inorganic fertiliser",1}, _xlpm.r, _xlpm.c))))</definedName>
+    <definedName name="RiceCultivation_SourceData.SourceData_RiceCultivation_OrganicAmendmentConversionFactor_Data">_xlfn.LAMBDA(
+    _xlfn.MAKEARRAY(7, 2,
+      _xlfn.LAMBDA(_xlpm.r,_xlpm.c,
+        INDEX({"Organic amendment i","CFOAi";"Straw incorporated shortly (&lt;30 days) before cultivation",1;"Straw incorporated long (&gt;30 days) before cultivation",0.19;"Compost",0.17;"Farm yard manure",0.21;"Green manure",0.45;"Inorganic fertiliser",1}, _xlpm.r, _xlpm.c)
+      )
+    )
+  )</definedName>
     <definedName name="RiceCultivation_SourceData.SourceData_RiceCultivation_OrganicAmendmentConversionFactor_Source">_xlfn.LAMBDA("VEERG 2026: Table A.2.3.3")</definedName>
     <definedName name="RiceCultivation_SourceData.SourceData_RiceCultivation_OrganicAmendmentConversionFactor_Title">_xlfn.LAMBDA("Conversion factor for organic amendment i")</definedName>
     <definedName name="RiceCultivation_SourceData.SourceData_RiceCultivation_OrganicAmendmentConversionFactor_Unit">_xlfn.LAMBDA("fraction")</definedName>
@@ -2364,6 +2396,126 @@
   <dxfs count="66">
     <dxf>
       <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -3223,126 +3375,6 @@
         <patternFill patternType="none">
           <fgColor indexed="64"/>
           <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -7034,26 +7066,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Home"/>
-      <sheetName val="Constants - Common"/>
-      <sheetName val="Acknowledgements"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
 <rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
   <global>
@@ -7132,7 +7144,7 @@
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{FE260FFD-8165-44FA-8171-CF7DA9E6EDC2}" name="Amendment mix name"/>
     <tableColumn id="2" xr3:uid="{1656D970-5568-46C3-8CF9-6544B58E60EE}" name="Straw added &lt; 30 days precultivation (t/ha)"/>
-    <tableColumn id="8" xr3:uid="{6AB8226E-B5ED-4236-BF1D-312497BC4C8F}" name="Straw added 30+ days pre cultivation (t/ha)" dataDxfId="53" dataCellStyle="Content normal"/>
+    <tableColumn id="8" xr3:uid="{6AB8226E-B5ED-4236-BF1D-312497BC4C8F}" name="Straw added 30+ days pre cultivation (t/ha)" dataDxfId="17" dataCellStyle="Content normal"/>
     <tableColumn id="3" xr3:uid="{7414D722-C23C-43BF-8BE4-9A787F770773}" name="Compost (t/ha)"/>
     <tableColumn id="4" xr3:uid="{10821F0A-FFAB-47C5-A2D8-0C77A91D1E11}" name="Farm yard manure (t/ha)"/>
     <tableColumn id="5" xr3:uid="{7554AF1F-8437-4EC1-A35B-D5ADAFFC9535}" name="Green manure (t/ha)"/>
@@ -7228,49 +7240,49 @@
     <tableColumn id="1" xr3:uid="{D01C89B8-460D-43FB-BC13-860F40EEDF57}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{D69D2743-DE4D-4C2E-897F-A682E4792E90}" name="MAT" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{D69D2743-DE4D-4C2E-897F-A682E4792E90}" name="MAT" totalsRowDxfId="53" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{43E94A14-ECA9-4D24-BD3B-6F90853F1623}" name="MAP" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
+    <tableColumn id="3" xr3:uid="{43E94A14-ECA9-4D24-BD3B-6F90853F1623}" name="MAP" totalsRowDxfId="52" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{0FFE5CEB-92B8-4F0C-954C-1654258B9009}" name="Frost days per year" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
+    <tableColumn id="4" xr3:uid="{0FFE5CEB-92B8-4F0C-954C-1654258B9009}" name="Frost days per year" totalsRowDxfId="51" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{EAE0BFB1-8A8D-4F76-AF2F-7F3A3F39AF16}" name="Elevation" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
+    <tableColumn id="5" xr3:uid="{EAE0BFB1-8A8D-4F76-AF2F-7F3A3F39AF16}" name="Elevation" totalsRowDxfId="50" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{7BF56A54-DEFF-4963-B9D8-1425EB5F5986}" name="MAP:PET" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
+    <tableColumn id="6" xr3:uid="{7BF56A54-DEFF-4963-B9D8-1425EB5F5986}" name="MAP:PET" totalsRowDxfId="49" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{D894A124-2A58-4A9A-81F0-270403516E8D}" name="Min temp" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
+    <tableColumn id="7" xr3:uid="{D894A124-2A58-4A9A-81F0-270403516E8D}" name="Min temp" totalsRowDxfId="48" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{281E5491-0322-4B39-91C1-808A9AA92DC9}" name="Max temp" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
+    <tableColumn id="8" xr3:uid="{281E5491-0322-4B39-91C1-808A9AA92DC9}" name="Max temp" totalsRowDxfId="47" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{549BB998-F7AA-41DD-9CD1-2547B6B5AE4E}" name="Min rainfall" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
+    <tableColumn id="9" xr3:uid="{549BB998-F7AA-41DD-9CD1-2547B6B5AE4E}" name="Min rainfall" totalsRowDxfId="46" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{29334872-89CD-401E-ABA5-8B865307D169}" name="Max rainfall" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
+    <tableColumn id="10" xr3:uid="{29334872-89CD-401E-ABA5-8B865307D169}" name="Max rainfall" totalsRowDxfId="45" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{34F87F29-D818-4C04-94C8-67D9646FCEA8}" name="Min frost days" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
+    <tableColumn id="11" xr3:uid="{34F87F29-D818-4C04-94C8-67D9646FCEA8}" name="Min frost days" totalsRowDxfId="44" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{BD42682C-5957-4823-B606-9612A785CCDC}" name="Max frost days" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
+    <tableColumn id="15" xr3:uid="{BD42682C-5957-4823-B606-9612A785CCDC}" name="Max frost days" totalsRowDxfId="43" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{82F25CB4-1EDC-46ED-8292-E152A1B2E2EF}" name="Min elevation" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
+    <tableColumn id="12" xr3:uid="{82F25CB4-1EDC-46ED-8292-E152A1B2E2EF}" name="Min elevation" totalsRowDxfId="42" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{B18A08B2-51EC-46CB-B531-47382F39C7F5}" name="Max elevation" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
+    <tableColumn id="16" xr3:uid="{B18A08B2-51EC-46CB-B531-47382F39C7F5}" name="Max elevation" totalsRowDxfId="41" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{0C71510E-74B2-4C70-BF53-A6CFF373D454}" name="Min MAP:PET" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
+    <tableColumn id="13" xr3:uid="{0C71510E-74B2-4C70-BF53-A6CFF373D454}" name="Min MAP:PET" totalsRowDxfId="40" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{C9B72C4B-BEDC-4438-867D-26385A49C0C7}" name="Max MAP:PET" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
+    <tableColumn id="17" xr3:uid="{C9B72C4B-BEDC-4438-867D-26385A49C0C7}" name="Max MAP:PET" totalsRowDxfId="39" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7288,7 +7300,7 @@
     <tableColumn id="1" xr3:uid="{0A9FF53A-8FDB-433E-8F42-964A381B2029}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{DF0F466D-B512-4631-8BDE-9FCCEFF29E7F}" name="Wet or Dry Zone" totalsRowDxfId="20" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{DF0F466D-B512-4631-8BDE-9FCCEFF29E7F}" name="Wet or Dry Zone" totalsRowDxfId="38" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7394,7 +7406,7 @@
     <tableColumn id="1" xr3:uid="{00936C20-2EF3-4B92-B727-606367DF7072}" name="Is in leaching zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{5827BEB9-27F5-4E79-98F3-336C5F4D89BD}" name="FracWET" dataDxfId="19">
+    <tableColumn id="2" xr3:uid="{5827BEB9-27F5-4E79-98F3-336C5F4D89BD}" name="FracWET" dataDxfId="37">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7415,7 +7427,7 @@
   </autoFilter>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{6CF21226-E2F8-4356-887C-701D50A69505}" name="Regime name"/>
-    <tableColumn id="7" xr3:uid="{03F35653-B2DB-4AB6-99EC-0912FB20CD21}" name="Area under cultivation (hectares)" dataDxfId="52" dataCellStyle="Content normal"/>
+    <tableColumn id="7" xr3:uid="{03F35653-B2DB-4AB6-99EC-0912FB20CD21}" name="Area under cultivation (hectares)" dataDxfId="16" dataCellStyle="Content normal"/>
     <tableColumn id="2" xr3:uid="{EA5A5A10-60BF-4C8A-8D3B-469871BE7F8E}" name="Pre-cultivation water regime (select)" dataCellStyle="Input select"/>
     <tableColumn id="3" xr3:uid="{85A41168-485F-4954-954D-E24F2E46EB1B}" name="Water regime (select)" dataCellStyle="Input select"/>
     <tableColumn id="4" xr3:uid="{EF7FE10B-862C-4478-9622-5C7E7DA42BCC}" name="Water regime sub-type (select)" dataCellStyle="Input select"/>
@@ -7466,7 +7478,7 @@
     <tableColumn id="1" xr3:uid="{8E925759-33F1-48CE-BF8F-1C907D56D334}" name="Irrigation type i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{2339A0A8-282A-4C1D-88CC-C91D7F7E2F90}" name="FracWET" dataDxfId="18" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{2339A0A8-282A-4C1D-88CC-C91D7F7E2F90}" name="FracWET" dataDxfId="36" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7484,7 +7496,7 @@
     <tableColumn id="1" xr3:uid="{D5BFF976-4AC1-486A-AC18-2703A0371049}" name="Climate zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{015C7263-11EF-4ECD-9A95-0D1FA0C0AB59}" name="EFPRP" dataDxfId="17" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{015C7263-11EF-4ECD-9A95-0D1FA0C0AB59}" name="EFPRP" dataDxfId="35" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7502,7 +7514,7 @@
     <tableColumn id="1" xr3:uid="{41D3FE7E-0B2A-4037-A526-EFC1F2E08083}" name="Month">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C860C210-84DC-4D57-B9B9-7A4B859E451A}" name="Season" dataDxfId="16" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{C860C210-84DC-4D57-B9B9-7A4B859E451A}" name="Season" dataDxfId="34" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7534,49 +7546,49 @@
     <tableColumn id="1" xr3:uid="{8C376FFF-40AA-4DB8-A527-41705B60404F}" name="Temperature zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{1E7E6284-EBB4-451D-8D4C-832725D2B9C3}" name="MAT (ºC)" dataDxfId="15" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{1E7E6284-EBB4-451D-8D4C-832725D2B9C3}" name="MAT (ºC)" dataDxfId="33" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{D0107B29-9381-4BAE-9EF3-8DD415DCC240}" name="Anaerobic lagoon" dataDxfId="14" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{D0107B29-9381-4BAE-9EF3-8DD415DCC240}" name="Anaerobic lagoon" dataDxfId="32" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{0CF5FFB0-89F9-4D73-A106-1F206160DD8D}" name="Digester / covered lagoons" dataDxfId="13" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{0CF5FFB0-89F9-4D73-A106-1F206160DD8D}" name="Digester / covered lagoons" dataDxfId="31" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{FFBEF878-F5C8-4B9F-9DA1-83090B244944}" name="Liquid systems" dataDxfId="12" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{FFBEF878-F5C8-4B9F-9DA1-83090B244944}" name="Liquid systems" dataDxfId="30" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{E88FABD7-C65C-4D77-AAEF-C1FF34A52E70}" name="Daily spread" dataDxfId="11" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{E88FABD7-C65C-4D77-AAEF-C1FF34A52E70}" name="Daily spread" dataDxfId="29" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{E4D0DC47-82D3-4078-A5F4-E10D80F4BB09}" name="Composting (passive windrow)" dataDxfId="10" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{E4D0DC47-82D3-4078-A5F4-E10D80F4BB09}" name="Composting (passive windrow)" dataDxfId="28" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{84369F6D-BF8F-4B6F-A75F-0BB8AD87CE06}" name="Solid storage" dataDxfId="9" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{84369F6D-BF8F-4B6F-A75F-0BB8AD87CE06}" name="Solid storage" dataDxfId="27" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{9CBC2428-99EF-43CB-96A1-6CFAE74657FD}" name="Pit storage" dataDxfId="8" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{9CBC2428-99EF-43CB-96A1-6CFAE74657FD}" name="Pit storage" dataDxfId="26" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{6C2A76DE-94DE-462A-91E6-585911BDFDF6}" name="Deep litter" dataDxfId="7" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{6C2A76DE-94DE-462A-91E6-585911BDFDF6}" name="Deep litter" dataDxfId="25" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{D7A8C618-0887-4C9A-B7CE-17EF1815BC38}" name="Poultry manure with bedding" dataDxfId="6" dataCellStyle="Content normal">
+    <tableColumn id="11" xr3:uid="{D7A8C618-0887-4C9A-B7CE-17EF1815BC38}" name="Poultry manure with bedding" dataDxfId="24" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{1BD1076A-5D5F-4F9C-8C93-E31281C4BA05}" name="Poultry manure without bedding" dataDxfId="5" dataCellStyle="Content normal">
+    <tableColumn id="12" xr3:uid="{1BD1076A-5D5F-4F9C-8C93-E31281C4BA05}" name="Poultry manure without bedding" dataDxfId="23" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{D7FB918E-84A7-4B01-BA09-6A6C6638801B}" name="Direct processing" dataDxfId="4" dataCellStyle="Content normal">
+    <tableColumn id="13" xr3:uid="{D7FB918E-84A7-4B01-BA09-6A6C6638801B}" name="Direct processing" dataDxfId="22" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{776C80DD-D7F4-47C0-9C8F-BA0150743FE8}" name="Direct application" dataDxfId="3" dataCellStyle="Content normal">
+    <tableColumn id="14" xr3:uid="{776C80DD-D7F4-47C0-9C8F-BA0150743FE8}" name="Direct application" dataDxfId="21" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{74216056-ABCD-44ED-9908-EFC45C6195BC}" name="Pasture range and paddock" dataDxfId="2" dataCellStyle="Content normal">
+    <tableColumn id="15" xr3:uid="{74216056-ABCD-44ED-9908-EFC45C6195BC}" name="Pasture range and paddock" dataDxfId="20" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{72CED5A5-B876-4EE2-96C8-518AB55ADE87}" name="MAT raw" dataDxfId="1" dataCellStyle="Content normal">
+    <tableColumn id="16" xr3:uid="{72CED5A5-B876-4EE2-96C8-518AB55ADE87}" name="MAT raw" dataDxfId="19" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7594,7 +7606,7 @@
     <tableColumn id="1" xr3:uid="{3AAE867B-DCF1-4C39-8857-BFEF63EF6146}" name="Climate Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{F37BF008-7DFA-40AA-984E-28E069D52595}" name="EFNi &amp; EFN2Oi" dataDxfId="0" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{F37BF008-7DFA-40AA-984E-28E069D52595}" name="EFNi &amp; EFN2Oi" dataDxfId="18" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7613,10 +7625,10 @@
     <tableColumn id="1" xr3:uid="{3A2980B6-3A2D-485C-8340-4AB52CBFBB99}" name="Water regime type">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(RiceCultivation_SourceData.SourceData_RiceCultivation_WaterScalingFactorGrowingSeason_Data(),Table_SourceData_WaterScalingFactorGrowingSeason[[#Headers],[Water regime type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{49BAF191-8DE2-478B-90F3-B9943FCEA9BA}" name="Water regime sub-type" dataDxfId="51" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{49BAF191-8DE2-478B-90F3-B9943FCEA9BA}" name="Water regime sub-type" dataDxfId="15" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(RiceCultivation_SourceData.SourceData_RiceCultivation_WaterScalingFactorGrowingSeason_Data(),Table_SourceData_WaterScalingFactorGrowingSeason[[#Headers],[Water regime type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{5202109C-BFD9-4463-9F2B-0B19C4500C07}" name="SFw" dataDxfId="50" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{5202109C-BFD9-4463-9F2B-0B19C4500C07}" name="SFw" dataDxfId="14" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(RiceCultivation_SourceData.SourceData_RiceCultivation_WaterScalingFactorGrowingSeason_Data(),Table_SourceData_WaterScalingFactorGrowingSeason[[#Headers],[Water regime type]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7634,7 +7646,7 @@
     <tableColumn id="1" xr3:uid="{FF0717D8-C262-491B-A316-62679EA1B7D7}" name="Water regime prior to cultivation">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(RiceCultivation_SourceData.SourceData_RiceCultivation_WaterScalingFactorPreSeason_Data(),Table_SourceData_WaterScalingFactorPreSeason[[#Headers],[Water regime prior to cultivation]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{3527B004-E130-4F0F-B6D1-0D475D57A7A4}" name="SFp" dataDxfId="49" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{3527B004-E130-4F0F-B6D1-0D475D57A7A4}" name="SFp" dataDxfId="13" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(RiceCultivation_SourceData.SourceData_RiceCultivation_WaterScalingFactorPreSeason_Data(),Table_SourceData_WaterScalingFactorPreSeason[[#Headers],[Water regime prior to cultivation]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7652,7 +7664,7 @@
     <tableColumn id="1" xr3:uid="{4FCCD68A-6FAE-4D17-88E1-28AE833F5E5E}" name="Organic amendment i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(RiceCultivation_SourceData.SourceData_RiceCultivation_OrganicAmendmentConversionFactor_Data(),Table15[[#Headers],[Organic amendment i]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{1F56CED6-01B8-4B36-AC56-E8A59F878F68}" name="CFOAi" dataDxfId="48" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{1F56CED6-01B8-4B36-AC56-E8A59F878F68}" name="CFOAi" dataDxfId="12" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(RiceCultivation_SourceData.SourceData_RiceCultivation_OrganicAmendmentConversionFactor_Data(),Table15[[#Headers],[Organic amendment i]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -10566,62 +10578,62 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F86">
-    <cfRule type="cellIs" dxfId="47" priority="62" operator="lessThan">
+    <cfRule type="cellIs" dxfId="11" priority="62" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F128:F129">
-    <cfRule type="cellIs" dxfId="46" priority="21" operator="lessThan">
+    <cfRule type="cellIs" dxfId="10" priority="21" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F140:F141">
-    <cfRule type="cellIs" dxfId="45" priority="20" operator="lessThan">
+    <cfRule type="cellIs" dxfId="9" priority="20" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F152:F153">
-    <cfRule type="cellIs" dxfId="44" priority="19" operator="lessThan">
+    <cfRule type="cellIs" dxfId="8" priority="19" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F164:F165">
-    <cfRule type="cellIs" dxfId="43" priority="18" operator="lessThan">
+    <cfRule type="cellIs" dxfId="7" priority="18" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F252:F253">
-    <cfRule type="cellIs" dxfId="42" priority="93" operator="lessThan">
+    <cfRule type="cellIs" dxfId="6" priority="93" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F257:F258">
-    <cfRule type="cellIs" dxfId="41" priority="92" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="92" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F262:F263">
-    <cfRule type="cellIs" dxfId="40" priority="91" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="91" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F286:F287">
-    <cfRule type="cellIs" dxfId="39" priority="85" operator="lessThan">
+    <cfRule type="cellIs" dxfId="3" priority="85" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F291:F292">
-    <cfRule type="cellIs" dxfId="38" priority="84" operator="lessThan">
+    <cfRule type="cellIs" dxfId="2" priority="84" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F296:F297">
-    <cfRule type="cellIs" dxfId="37" priority="83" operator="lessThan">
+    <cfRule type="cellIs" dxfId="1" priority="83" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J211 E212:I212">
-    <cfRule type="cellIs" dxfId="36" priority="79" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="79" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16821,6 +16833,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -17015,20 +17036,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACkAKgAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADIAKQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAHQAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAC8AdABcAHUAMAAwADMAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAdQAwADAAMgA3AFwAIgAgAFwAdQAwADAAMgA2ACAAcwBoACAAXAB1ADAAMAAyADYAIABcACIAXAB1ADAAMAAyADcAIQBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFUATgBEACgAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIAAwACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAE0ATQBTACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAaQB0AGwAZQBDAGUAbABsACwAIABTAG8AdQByAGMAZQBDAGUAbABsACwAXABuACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAEwARQBGAFQAKABTAG8AdQByAGMAZQBDAGUAbABsACwAIABGAEkATgBEACgAXAAiACwAXAAiACwAIABTAG8AdQByAGMAZQBDAGUAbABsACkAIAAtADEAKQAsACAAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFwAIgAsACAAXAAiAFwAIgApACAAXAB1ADAAMAAyADYAIABcACIAIABcACIAIABcAHUAMAAwADIANgAgAFQAaQB0AGwAZQBDAGUAbABsAFwAbgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBTAGMAYQBsAGkAbgBnACAAZgBhAGMAdABvAHIAIABiAGEAcwBlAGQAIABvAG4AIAB0AGgAZQAgAHcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAZQBtAHAAbABvAHkAZQBkACAAZAB1AHIAaQBuAGcAIAB0AGgAZQAgAGcAcgBvAHcAaQBuAGcAIABzAGUAYQBzAG8AbgAgAGMAdQBsAHQAaQB2AGEAdABpAG8AbgAgAHAAZQByAGkAbwBkAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBTAEYAdwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADMALgAxAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAdAB5AHAAZQBcACIALAAgAFwAIgBXAGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAHMAdQBiACAALQAgAHQAeQBwAGUAXAAiACwAIABcACIAUwBGAHcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFUAcABsAGEAbgBkAFwAIgAsACAAXAAiAFAAYQBkAGQAeQAgAHIAbwB0AGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVQBwAGwAYQBuAGQAXAAiACwAIABcACIARgBhAGwAbABvAHcAIAB3AGkAdABoAG8AdQB0ACAAZgBsAG8AbwBkAGkAbgBnACAAaQBuACAAcAByAGUAdgBpAG8AdQBzACAAeQBlAGEAcgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQwBvAG4AdABpAG4AdQBvAHUAcwBsAHkAIABmAGwAbwBvAGQAZQBkAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAgAHAAZQByAGkAbwBkAFwAIgAsACAAMAAuADcAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBNAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUAIABwAGUAcgBpAG8AZABzAFwAIgAsACAAMAAuADUANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAZQBkACAAYQBuAGQAIABkAGUAZQBwACAAdwBhAHQAZQByAFwAIgAsACAAXAAiAFIAZQBnAHUAbABhAHIAIAByAGEAaQBuAGYAZQBkAFwAIgAsACAAMAAuADUANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAZQBkACAAYQBuAGQAIABkAGUAZQBwACAAdwBhAHQAZQByAFwAIgAsACAAXAAiAEQAcgBvAHUAZwBoAHQAIABwAHIAbwBuAGUAXAAiACwAIAAwAC4AMQA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAYQBpAG4AZgBlAGQAIABhAG4AZAAgAGQAZQBlAHAAIAB3AGEAdABlAHIAXAAiACwAIABcACIARABlAGUAcAAgAHcAYQB0AGUAcgBcACIALAAgADAALgAwADYAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMAYwBhAGwAaQBuAGcAIABmAGEAYwB0AG8AcgAgAGIAYQBzAGUAZAAgAG8AbgAgAHQAaABlACAAdwBhAHQAZQByACAAcgBlAGcAaQBtAGUAIABlAG0AcABsAG8AeQBlAGQAIABpAG4AIAB0AGgAZQAgAHAAcgBlACAALQAgAHMAZQBhAHMAbwBuACAAYgBlAGYAbwByAGUAIAB0AGgAZQAgAGcAcgBvAHcAaQBuAGcAIABwAGUAcgBpAG8AZABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMARgBwAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBQAHIAZQBTAGUAYQBzAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAzAC4AMgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAcAByAGkAbwByACAAdABvACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuACAAcABlAHIAaQBvAGQAIABwAFwAIgAsACAAXAAiAFMARgBwAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAgAGYAbABvAG8AZABlAGQAIABwAHIAZQAtAHMAZQBhAHMAbwBuACAAXAB1ADAAMAAzAGMAMQA4ADAAIABkAGEAeQBzAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAgAGYAbABvAG8AZABlAGQAIABwAHIAZQAtAHMAZQBhAHMAbwBuACAAXAB1ADAAMAAzAGUAMQA4ADAAIABkAGEAeQBzAFwAIgAsACAAMAAuADgAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGwAbwBvAGQAZQBkACAAcAByAGUALQBzAGUAYQBzAG8AbgAgAFwAdQAwADAAMwBlADMAMAAgAGQAYQB5AHMAXAAiACwAIAAyAC4ANAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AZgBsAG8AbwBkAGUAZAAgAHAAcgBlAC0AcwBlAGEAcwBvAG4AIABcAHUAMAAwADMAZQAzADYANQAgAGQAYQB5AHMAXAAiACwAIAAwAC4ANQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAIABpAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMARgBPAEEAaQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAzAC4AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAGMAbAB1AGQAZQBkACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBzACAAYQBtAGUAbgBkAG0AZQBuAHQAIABhAHMAIABwAGUAcgAgAFYARQBFAFIARwAgAGUAcQB1AGEAdABpAG8AbgAgAGQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGgAZQByAGUAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABpAHMAIABhAHAAcABsAGkAZQBkACAAdABvACAAdABoAGUAIAByAGkAYwBlACAAZgBpAGUAbABkAHMAIAByAGEAdABoAGUAcgAgAHQAaABhAG4AIABvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAcwAsACAAUwBGAF8AbwAgAGkAcwAgAHMAZQB0ACAAdABvACAAMQAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADcALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdAAgAGkAXAAiACwAIABcACIAQwBGAE8AQQBpAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAcgBhAHcAIABpAG4AYwBvAHIAcABvAHIAYQB0AGUAZAAgAHMAaABvAHIAdABsAHkAIAAoAFwAdQAwADAAMwBjADMAMAAgAGQAYQB5AHMAKQAgAGIAZQBmAG8AcgBlACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAIgAsACAAMQAuADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAcgBhAHcAIABpAG4AYwBvAHIAcABvAHIAYQB0AGUAZAAgAGwAbwBuAGcAIAAoAFwAdQAwADAAMwBlADMAMAAgAGQAYQB5AHMAKQAgAGIAZQBmAG8AcgBlACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAIgAsACAAMAAuADEAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbQBwAG8AcwB0AFwAIgAsACAAMAAuADEANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGEAcgBtACAAeQBhAHIAZAAgAG0AYQBuAHUAcgBlAFwAIgAsACAAMAAuADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAHIAZQBlAG4AIABtAGEAbgB1AHIAZQBcACIALAAgADAALgA0ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEIAYQBzAGUAbABpAG4AZQBFAEYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQgBhAHMAZQBsAGkAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGMAbwBuAHQAaQBuAHUAbwB1AHMAbAB5ACAAZgBsAG8AbwBkAGUAZAAgAGYAaQBlAGwAZABzACAAdwBpAHQAaABvAHUAdAAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdABzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYAYwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAEMASAA0ACAALwAgAGgAYQAgAC8AIABkAGEAeQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA3AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAxAC4AMQA5ACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADcALgAxADoAIABSAGkAYwBlACAAQwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA3AC4AMQAuADEALgAxACAATQBlAHQAaABvAGQAIAAxACAALQAgAFIAaQBjAGUAIABDAHUAbAB0AGkAdgBhAHQAaQBvAG4AIABDAEgANAAgAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBcAG4ATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHIAaQBjAGUAIABjAHUAbAB0AGkAdgBhAHQAaQBvAG4AXABuAEUAXwByAGkAYwBlAFwAbgB0ACAAQwBIADQAXABuAEUAXwB7AHIAaQBjAGUAfQA9AFwAXABzAHUAbQBfAHcAXABcAHMAdQBtAF8AcABcAFwAcwB1AG0AXwBvACgAQQBfAHsAcgBpAGMAZQAsAHcAcABvAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAcgBpAGMAZQAsAHcAcABvAH0AXABcAHQAaQBtAGUAcwAgAHQAXwB7AHIAaQBjAGUALAB3AHAAbwB9ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXABuAEEAXwByAGkAYwBlAHcAcABvACAAPQAgAGEAbgBuAHUAYQBsACAAYQByAGUAYQAgAG8AZgAgAHIAaQBjAGUAIABjAHUAbAB0AGkAdgBhAHQAaQBvAG4AIAB1AG4AZABlAHIAIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAHcALAAgAHAAcgBlAC0AcwBlAGEAcwBvAG4AIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAHAALAAgAGEAbgBkACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0ACAAYwBvAG4AZABpAHQAaQBvAG4AIABvACAAKABoAGEAKQBcAG4ARQBGAF8AcgBpAGMAZQB3AHAAbwAgAD0AIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcgBpAGMAZQAgAGMAdQBsAHQAaQB2AGEAdABpAG8AbgAgAHUAbgBkAGUAcgAgAGMAbwBuAGQAaQB0AGkAbwBuAHMAIAB3ACwAIABwACwAIABhAG4AZAAgAG8AIAAoAGsAZwAgAEMASAA0AC8AaABhAC8AZABhAHkAKQBcAG4AdABfAHIAaQBjAGUAdwBwAG8AIAA9ACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuACAAcABlAHIAaQBvAGQAIABmAG8AcgAgAHIAaQBjAGUAIAB1AG4AZABlAHIAIABjAG8AbgBkAGkAdABpAG8AbgBzACAAdwAsACAAcAAsACAAYQBuAGQAIABvACAAKABkAGEAeQBzACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAF8AcgBpAGMAZQB3AHAAbwAsACAARQBGAF8AcgBpAGMAZQB3AHAAbwAsACAAdABfAHIAaQBjAGUAdwBwAG8ALABcAG4AIAAgACAAIABTAFUATQAoAEEAXwByAGkAYwBlAHcAcABvACAAKgAgAEUARgBfAHIAaQBjAGUAdwBwAG8AIAAqACAAdABfAHIAaQBjAGUAdwBwAG8AKQAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHIAaQBjAGUAIABjAHUAbAB0AGkAdgBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwByAGkAYwBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMASAA0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADcALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsAcgBpAGMAZQB9AD0AXABcAHMAdQBtAF8AdwBcAFwAcwB1AG0AXwBwAFwAXABzAHUAbQBfAG8AKABBAF8AewByAGkAYwBlACwAdwBwAG8AfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewByAGkAYwBlACwAdwBwAG8AfQBcAFwAdABpAG0AZQBzACAAdABfAHsAcgBpAGMAZQAsAHcAcABvAH0AKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAF8AcgBpAGMAZQB3AHAAbwBcACIALAAgAFwAIgBhAG4AbgB1AGEAbAAgAGEAcgBlAGEAIABvAGYAIAByAGkAYwBlACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuACAAdQBuAGQAZQByACAAdwBhAHQAZQByACAAcgBlAGcAaQBtAGUAIAB3ACwAIABwAHIAZQAtAHMAZQBhAHMAbwBuACAAdwBhAHQAZQByACAAcgBlAGcAaQBtAGUAIABwACwAIABhAG4AZAAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdAAgAGMAbwBuAGQAaQB0AGkAbwBuACAAbwBcACIALAAgAFwAIgBoAGEAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwByAGkAYwBlAHcAcABvAFwAIgAsACAAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAByAGkAYwBlACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuACAAdQBuAGQAZQByACAAYwBvAG4AZABpAHQAaQBvAG4AcwAgAHcALAAgAHAALAAgAGEAbgBkACAAbwBcACIALAAgAFwAIgBrAGcAIABDAEgANAAvAGgAYQAvAGQAYQB5AFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANwAuADEALgAxAC4AMQAsACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHQAXwByAGkAYwBlAHcAcABvAFwAIgAsACAAXAAiAGMAdQBsAHQAaQB2AGEAdABpAG8AbgAgAHAAZQByAGkAbwBkACAAZgBvAHIAIAByAGkAYwBlACAAdQBuAGQAZQByACAAYwBvAG4AZABpAHQAaQBvAG4AcwAgAHcALAAgAHAALAAgAGEAbgBkACAAbwBcACIALAAgAFwAIgBkAGEAeQBzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcwBcACIALAAgAFwAIgBuAHUAbQBiAGUAcgAgAG8AZgAgAGMAcgBvAHAAcABpAG4AZwAgAHMAZQBhAHMAbwBuAHMAIABpAG4AIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAbQBhAG4AYQBnAGUAZAAgAHQAaABpAHMAIAB3AGEAeQBcACIALAAgAFwAIgBzAGUAYQBzAG8AbgBzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAbgB1AG0AYgBlAHIAIABvAGYAIABzAGUAYQBzAG8AbgBzAFwAdQAwADAAMgA3ACAAdgBhAHIAaQBhAGIAbABlACAAYQBzACAAcABlAHIAIABWAEUARQBSAEcAIABkAGUAcwBjAHIAaQBwAHQAaQBvAG4AIABpAG4AIAA3AC4AMgAuADEAIABcAHUAMAAwADIANwBXAGgAZQByAGUAIAB0AGgAZQByAGUAIABpAHMAIABtAG8AcgBlACAAdABoAGEAbgAgAG8AbgBlACAAYwByAG8AcABwAGkAbgBnACAAcwBlAGEAcwBvAG4AIABwAGUAcgAgAHkAZQBhAHIALAAgAEEAcgBpAGMAZQAsAHcAcABvACAAcwBoAGEAbABsACAAYgBlACAAcwBjAGEAbABlAGQAIABhAGMAYwBvAHIAZABpAG4AZwBsAHkAXAB1ADAAMAAyADcAXAAiACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAbgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcgBpAGMAZQAgAGMAdQBsAHQAaQB2AGEAdABpAG8AbgBcAG4ARQBGAF8AcgBpAGMAZQB3AHAAbwBcAG4AawBnACAAQwBIADQALwBoAGEALwBkAGEAeQBcAG4ARQBGAF8AewByAGkAYwBlACwAdwBwAG8AfQA9AEUARgBfAGMAXABcAHQAaQBtAGUAcwAgAFMARgBfAHcAXABcAHQAaQBtAGUAcwAgAFMARgBfAHAAXABcAHQAaQBtAGUAcwAgAFMARgBfAG8AXABuAEUARgBfAGMAIAA9ACAAYgBhAHMAZQBsAGkAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGMAbwBuAHQAaQBuAHUAbwB1AHMAbAB5ACAAZgBsAG8AbwBkAGUAZAAgAGYAaQBlAGwAZABzACAAdwBpAHQAaABvAHUAdAAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdABzACAAKABrAGcAIABDAEgANAAvAGgAYQAvAGQAYQB5ACkAXABuAFMARgBfAHcAIAA9ACAAcwBjAGEAbABpAG4AZwAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAGQAdQByAGkAbgBnACAAdABoAGUAIABnAHIAbwB3AGkAbgBnACAAcwBlAGEAcwBvAG4AXABuAFMARgBfAHAAIAA9ACAAcwBjAGEAbABpAG4AZwAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAGkAbgAgAHQAaABlACAAcAByAGUALQBzAGUAYQBzAG8AbgBcAG4AUwBGAF8AbwAgAD0AIABzAGMAYQBsAGkAbgBnACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAeQBwAGUAIABhAG4AZAAgAGEAbQBvAHUAbgB0ACAAbwBmACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0AHMAIAAoAHMAZQB0ACAAdABvACAAMQAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdQBzAGUAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUARgBfAGMALAAgAFMARgBfAHcALAAgAFMARgBfAHAALAAgAFMARgBfAG8ALABcAG4AIAAgACAAIABFAEYAXwBjACAAKgAgAFMARgBfAHcAIAAqACAAUwBGAF8AcAAgACoAIABTAEYAXwBvAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHIAaQBjAGUAIABjAHUAbAB0AGkAdgBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUARgBfAHIAaQBjAGUAdwBwAG8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABDAEgANAAvAGgAYQAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADcALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAF8AewByAGkAYwBlACwAdwBwAG8AfQA9AEUARgBfAGMAXABcAHQAaQBtAGUAcwAgAFMARgBfAHcAXABcAHQAaQBtAGUAcwAgAFMARgBfAHAAXABcAHQAaQBtAGUAcwAgAFMARgBfAG8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADcALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AYwBcACIALAAgAFwAIgBiAGEAcwBlAGwAaQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAYwBvAG4AdABpAG4AdQBvAHUAcwBsAHkAIABmAGwAbwBvAGQAZQBkACAAZgBpAGUAbABkAHMAIAB3AGkAdABoAG8AdQB0ACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0AHMAXAAiACwAIABcACIAawBnACAAQwBIADQALwBoAGEALwBkAGEAeQBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgBfAHcAXAAiACwAIABcACIAcwBjAGEAbABpAG4AZwAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAGQAdQByAGkAbgBnACAAdABoAGUAIABnAHIAbwB3AGkAbgBnACAAcwBlAGEAcwBvAG4AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBGAF8AcABcACIALAAgAFwAIgBzAGMAYQBsAGkAbgBnACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAaQBuACAAdABoAGUAIABwAHIAZQAtAHMAZQBhAHMAbwBuAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgBfAG8AXAAiACwAIABcACIAcwBjAGEAbABpAG4AZwAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHkAcABlACAAYQBuAGQAIABhAG0AbwB1AG4AdAAgAG8AZgAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdABzAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADcALgAxAC4AMQAuADEALAAgACgAMwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgB3AFwAIgAsACAAXAAiAHcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAZAB1AHIAaQBuAGcAIABnAHIAbwB3AGkAbgBnACAAcwBlAGEAcwBvAG4AXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBwAFwAIgAsACAAXAAiAHAAcgBlAC0AcwBlAGEAcwBvAG4AIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAG8AXAAiACwAIABcACIAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0AFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXABuAE8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdABzACAAcwBjAGEAbABpAG4AZwAgAGYAYQBjAHQAbwByAFwAbgBTAEYAXwBvAFwAbgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAbgBTAEYAXwBvAD0AKAAxACsAXABcAHMAdQBtAF8AbwAoAFIATwBBAF8AbwBcAFwAdABpAG0AZQBzACAAQwBGAE8AQQBfAG8AKQApAF4AewAwAC4ANQA5AH0AXABuAFIATwBBAF8AbwAgAD0AIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAByAGEAdABlACAAbwBmACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0ACAAbwAgACgAdABvAG4AbgBlAHMALwBoAGEAKQBcAG4AQwBGAE8AQQBfAG8AIAA9ACAAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAbwBmACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0ACAAbwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUgBPAEEAXwBvACwAIABDAEYATwBBAF8AbwAsAFwAbgAgACAAIAAgACgAMQAgACsAIABTAFUATQAoAFIATwBBAF8AbwAgACoAIABDAEYATwBBAF8AbwApACkAIABeACAAMAAuADUAOQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABSAE8AQQBfAG8AMQAsACAAQwBGAE8AQQBfAG8AMQAsACAAUgBPAEEAXwBvADIALAAgAEMARgBPAEEAXwBvADIALAAgAFIATwBBAF8AbwAzACwAIABDAEYATwBBAF8AbwAzACwAIABSAE8AQQBfAG8ANAAsACAAQwBGAE8AQQBfAG8ANAAsACAAUgBPAEEAXwBvADUALAAgAEMARgBPAEEAXwBvADUALAAgAFIATwBBAF8AbwA2ACwAIABDAEYATwBBAF8AbwA2ACwAXABuACAAIAAgACAAKAAxACAAKwAgACgAKABSAE8AQQBfAG8AMQAgACoAIABDAEYATwBBAF8AbwAxACkAIAArACAAKABSAE8AQQBfAG8AMgAgACoAIABDAEYATwBBAF8AbwAyACkAIAArACAAKABSAE8AQQBfAG8AMwAgACoAIABDAEYATwBBAF8AbwAzACkAKwAgACgAUgBPAEEAXwBvADQAIAAqACAAQwBGAE8AQQBfAG8ANAApACAAKwAgACgAUgBPAEEAXwBvADUAIAAqACAAQwBGAE8AQQBfAG8ANQApACAAKwAgACgAUgBPAEEAXwBvADYAIAAqACAAQwBGAE8AQQBfAG8ANgApACkAKQAgAF4AIAAwAC4ANQA5AFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBPAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAcwAgAHMAYwBhAGwAaQBuAGcAIABmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBTAEYAXwBvAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANwAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAzACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAUwBGAF8AbwA9ACgAMQArAFwAXABzAHUAbQBfAG8AUgBPAEEAXwBvAFwAXAB0AGkAbQBlAHMAIABDAEYATwBBAF8AbwApAF4AewAwAC4ANQA5AH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMARgBfAG8APQAoADEAKwAgACgAKABSAE8AQQBfAG8AMQBcAFwAdABpAG0AZQBzACAAQwBGAE8AQQBfAG8AMQApACAAKwAgACgAUgBPAEEAXwBvADIAXABcAHQAaQBtAGUAcwAgAEMARgBPAEEAXwBvADIAKQAgACsAIAAoAFIATwBBAF8AbwAzAFwAXAB0AGkAbQBlAHMAIABDAEYATwBBAF8AbwAzACkAIAArACAAKABSAE8AQQBfAG8ANABcAFwAdABpAG0AZQBzACAAQwBGAE8AQQBfAG8ANAApACAAKwAgACgAUgBPAEEAXwBvADUAXABcAHQAaQBtAGUAcwAgAEMARgBPAEEAXwBvADUAKQAgACsAIAAoAFIATwBBAF8AbwA2AFwAXAB0AGkAbQBlAHMAIABDAEYATwBBAF8AbwA2ACkAKQBeAHsAMAAuADUAOQB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBPAEEAXwBvAFwAIgAsACAAXAAiAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHIAYQB0AGUAIABvAGYAIABvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAIABvAFwAIgAsACAAXAAiAHQAbwBuAG4AZQBzAC8AaABhAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBGAE8AQQBfAG8AXAAiACwAIABcACIAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAbwBmACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0ACAAbwBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBvAFwAIgAsACAAXAAiAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdAAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAGMAbAB1AGQAZQBkACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBzACAAYQBtAGUAbgBkAG0AZQBuAHQAIABhAHMAIABwAGUAcgAgAFYARQBFAFIARwAgAGUAcQB1AGEAdABpAG8AbgAgAGQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGgAZQByAGUAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABpAHMAIABhAHAAcABsAGkAZQBkACAAdABvACAAdABoAGUAIAByAGkAYwBlACAAZgBpAGUAbABkAHMAIAByAGEAdABoAGUAcgAgAHQAaABhAG4AIABvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAcwAsACAAUwBGAF8AbwAgAGkAcwAgAHMAZQB0ACAAdABvACAAMQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGUAYwBsAGEAcgBlAGQAIABlAGEAYwBoACAAYQBtAGUAbgBkAG0AZQBuAHQAIABzAGUAcABhAHIAYQB0AGUAbAB5ACAAdABvACAAYQBsAGwAbwB3ACAAcwB1AG0AbQBpAG4AZwAgAGkAbgAgAEUAeABjAGUAbAAgAGkAbgAgAG8AbgBlACAAZQBxAHUAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgAiAH0AXQAsACIAcAByAG8AagBlAGMAdABOAGEAbQBlAHMAIgA6AFsAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAEcAcgBvAHcAaQBuAGcAUwBlAGEAcwBvAG4AXwBVAG4AaQB0ACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAEcAcgBvAHcAaQBuAGcAUwBlAGEAcwBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAEQAYQB0AGEAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBUAGkAdABsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBVAG4AaQB0ACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBQAHIAZQBTAGUAYQBzAG8AbgBfAEQAYQB0AGEAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVABpAHQAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBVAG4AaQB0ACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFMAbwB1AHIAYwBlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAEQAYQB0AGEAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAFQAaQB0AGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEIAYQBzAGUAbABpAG4AZQBFAEYAXwBVAG4AaQB0ACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEIAYQBzAGUAbABpAG4AZQBFAEYAXwBTAG8AdQByAGMAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAEQAYQB0AGEAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBUAGkAdABsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AVQBuAGkAdAAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
@@ -17039,7 +17047,19 @@
 </p:properties>
 </file>
 
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACkAKgAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADIAKQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAHQAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAC8AdABcAHUAMAAwADMAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAdQAwADAAMgA3AFwAIgAgAFwAdQAwADAAMgA2ACAAcwBoACAAXAB1ADAAMAAyADYAIABcACIAXAB1ADAAMAAyADcAIQBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFUATgBEACgAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIAAwACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEkATgAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0AQQBYACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAE0ATQBTACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUgBlAHMAdQBsAHQAcwBJAHQAZQBtAEYAcgBvAG0ARQBxAHUAYQB0AGkAbwBuAFQAaQB0AGwAZQBBAG4AZABTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAaQB0AGwAZQBDAGUAbABsACwAIABTAG8AdQByAGMAZQBDAGUAbABsACwAXABuACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAEwARQBGAFQAKABTAG8AdQByAGMAZQBDAGUAbABsACwAIABGAEkATgBEACgAXAAiACwAXAAiACwAIABTAG8AdQByAGMAZQBDAGUAbABsACkAIAAtADEAKQAsACAAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFwAIgAsACAAXAAiAFwAIgApACAAXAB1ADAAMAAyADYAIABcACIAIABcACIAIABcAHUAMAAwADIANgAgAFQAaQB0AGwAZQBDAGUAbABsAFwAbgApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBTAGMAYQBsAGkAbgBnACAAZgBhAGMAdABvAHIAIABiAGEAcwBlAGQAIABvAG4AIAB0AGgAZQAgAHcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAZQBtAHAAbABvAHkAZQBkACAAZAB1AHIAaQBuAGcAIAB0AGgAZQAgAGcAcgBvAHcAaQBuAGcAIABzAGUAYQBzAG8AbgAgAGMAdQBsAHQAaQB2AGEAdABpAG8AbgAgAHAAZQByAGkAbwBkAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBTAEYAdwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADMALgAxAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAdAB5AHAAZQBcACIALAAgAFwAIgBXAGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAHMAdQBiACAALQAgAHQAeQBwAGUAXAAiACwAIABcACIAUwBGAHcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFUAcABsAGEAbgBkAFwAIgAsACAAXAAiAFAAYQBkAGQAeQAgAHIAbwB0AGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVQBwAGwAYQBuAGQAXAAiACwAIABcACIARgBhAGwAbABvAHcAIAB3AGkAdABoAG8AdQB0ACAAZgBsAG8AbwBkAGkAbgBnACAAaQBuACAAcAByAGUAdgBpAG8AdQBzACAAeQBlAGEAcgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQwBvAG4AdABpAG4AdQBvAHUAcwBsAHkAIABmAGwAbwBvAGQAZQBkAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAgAHAAZQByAGkAbwBkAFwAIgAsACAAMAAuADcAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBNAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUAIABwAGUAcgBpAG8AZABzAFwAIgAsACAAMAAuADUANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAZQBkACAAYQBuAGQAIABkAGUAZQBwACAAdwBhAHQAZQByAFwAIgAsACAAXAAiAFIAZQBnAHUAbABhAHIAIAByAGEAaQBuAGYAZQBkAFwAIgAsACAAMAAuADUANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAZQBkACAAYQBuAGQAIABkAGUAZQBwACAAdwBhAHQAZQByAFwAIgAsACAAXAAiAEQAcgBvAHUAZwBoAHQAIABwAHIAbwBuAGUAXAAiACwAIAAwAC4AMQA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAYQBpAG4AZgBlAGQAIABhAG4AZAAgAGQAZQBlAHAAIAB3AGEAdABlAHIAXAAiACwAIABcACIARABlAGUAcAAgAHcAYQB0AGUAcgBcACIALAAgADAALgAwADYAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMAYwBhAGwAaQBuAGcAIABmAGEAYwB0AG8AcgAgAGIAYQBzAGUAZAAgAG8AbgAgAHQAaABlACAAdwBhAHQAZQByACAAcgBlAGcAaQBtAGUAIABlAG0AcABsAG8AeQBlAGQAIABpAG4AIAB0AGgAZQAgAHAAcgBlACAALQAgAHMAZQBhAHMAbwBuACAAYgBlAGYAbwByAGUAIAB0AGgAZQAgAGcAcgBvAHcAaQBuAGcAIABwAGUAcgBpAG8AZABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMARgBwAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBQAHIAZQBTAGUAYQBzAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAzAC4AMgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAcAByAGkAbwByACAAdABvACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuACAAcABlAHIAaQBvAGQAIABwAFwAIgAsACAAXAAiAFMARgBwAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAgAGYAbABvAG8AZABlAGQAIABwAHIAZQAtAHMAZQBhAHMAbwBuACAAXAB1ADAAMAAzAGMAMQA4ADAAIABkAGEAeQBzAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAgAGYAbABvAG8AZABlAGQAIABwAHIAZQAtAHMAZQBhAHMAbwBuACAAXAB1ADAAMAAzAGUAMQA4ADAAIABkAGEAeQBzAFwAIgAsACAAMAAuADgAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGwAbwBvAGQAZQBkACAAcAByAGUALQBzAGUAYQBzAG8AbgAgAFwAdQAwADAAMwBlADMAMAAgAGQAYQB5AHMAXAAiACwAIAAyAC4ANAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AZgBsAG8AbwBkAGUAZAAgAHAAcgBlAC0AcwBlAGEAcwBvAG4AIABcAHUAMAAwADMAZQAzADYANQAgAGQAYQB5AHMAXAAiACwAIAAwAC4ANQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAIABpAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMARgBPAEEAaQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAzAC4AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAGMAbAB1AGQAZQBkACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBzACAAYQBtAGUAbgBkAG0AZQBuAHQAIABhAHMAIABwAGUAcgAgAFYARQBFAFIARwAgAGUAcQB1AGEAdABpAG8AbgAgAGQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGgAZQByAGUAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABpAHMAIABhAHAAcABsAGkAZQBkACAAdABvACAAdABoAGUAIAByAGkAYwBlACAAZgBpAGUAbABkAHMAIAByAGEAdABoAGUAcgAgAHQAaABhAG4AIABvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAcwAsACAAUwBGAF8AbwAgAGkAcwAgAHMAZQB0ACAAdABvACAAMQAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADcALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdAAgAGkAXAAiACwAIABcACIAQwBGAE8AQQBpAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAcgBhAHcAIABpAG4AYwBvAHIAcABvAHIAYQB0AGUAZAAgAHMAaABvAHIAdABsAHkAIAAoAFwAdQAwADAAMwBjADMAMAAgAGQAYQB5AHMAKQAgAGIAZQBmAG8AcgBlACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAIgAsACAAMQAuADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAcgBhAHcAIABpAG4AYwBvAHIAcABvAHIAYQB0AGUAZAAgAGwAbwBuAGcAIAAoAFwAdQAwADAAMwBlADMAMAAgAGQAYQB5AHMAKQAgAGIAZQBmAG8AcgBlACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAIgAsACAAMAAuADEAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbQBwAG8AcwB0AFwAIgAsACAAMAAuADEANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGEAcgBtACAAeQBhAHIAZAAgAG0AYQBuAHUAcgBlAFwAIgAsACAAMAAuADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAHIAZQBlAG4AIABtAGEAbgB1AHIAZQBcACIALAAgADAALgA0ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEIAYQBzAGUAbABpAG4AZQBFAEYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQgBhAHMAZQBsAGkAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGMAbwBuAHQAaQBuAHUAbwB1AHMAbAB5ACAAZgBsAG8AbwBkAGUAZAAgAGYAaQBlAGwAZABzACAAdwBpAHQAaABvAHUAdAAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdABzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYAYwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAEMASAA0ACAALwAgAGgAYQAgAC8AIABkAGEAeQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA3AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAxAC4AMQA5ACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADcALgAxADoAIABSAGkAYwBlACAAQwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA3AC4AMQAuADEALgAxACAATQBlAHQAaABvAGQAIAAxACAALQAgAFIAaQBjAGUAIABDAHUAbAB0AGkAdgBhAHQAaQBvAG4AIABDAEgANAAgAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBcAG4ATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHIAaQBjAGUAIABjAHUAbAB0AGkAdgBhAHQAaQBvAG4AXABuAEUAXwByAGkAYwBlAFwAbgB0ACAAQwBIADQAXABuAEUAXwB7AHIAaQBjAGUAfQA9AFwAXABzAHUAbQBfAHcAXABcAHMAdQBtAF8AcABcAFwAcwB1AG0AXwBvACgAQQBfAHsAcgBpAGMAZQAsAHcAcABvAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAcgBpAGMAZQAsAHcAcABvAH0AXABcAHQAaQBtAGUAcwAgAHQAXwB7AHIAaQBjAGUALAB3AHAAbwB9ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXABuAEEAXwByAGkAYwBlAHcAcABvACAAPQAgAGEAbgBuAHUAYQBsACAAYQByAGUAYQAgAG8AZgAgAHIAaQBjAGUAIABjAHUAbAB0AGkAdgBhAHQAaQBvAG4AIAB1AG4AZABlAHIAIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAHcALAAgAHAAcgBlAC0AcwBlAGEAcwBvAG4AIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAHAALAAgAGEAbgBkACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0ACAAYwBvAG4AZABpAHQAaQBvAG4AIABvACAAKABoAGEAKQBcAG4ARQBGAF8AcgBpAGMAZQB3AHAAbwAgAD0AIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcgBpAGMAZQAgAGMAdQBsAHQAaQB2AGEAdABpAG8AbgAgAHUAbgBkAGUAcgAgAGMAbwBuAGQAaQB0AGkAbwBuAHMAIAB3ACwAIABwACwAIABhAG4AZAAgAG8AIAAoAGsAZwAgAEMASAA0AC8AaABhAC8AZABhAHkAKQBcAG4AdABfAHIAaQBjAGUAdwBwAG8AIAA9ACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuACAAcABlAHIAaQBvAGQAIABmAG8AcgAgAHIAaQBjAGUAIAB1AG4AZABlAHIAIABjAG8AbgBkAGkAdABpAG8AbgBzACAAdwAsACAAcAAsACAAYQBuAGQAIABvACAAKABkAGEAeQBzACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAF8AcgBpAGMAZQB3AHAAbwAsACAARQBGAF8AcgBpAGMAZQB3AHAAbwAsACAAdABfAHIAaQBjAGUAdwBwAG8ALABcAG4AIAAgACAAIABTAFUATQAoAEEAXwByAGkAYwBlAHcAcABvACAAKgAgAEUARgBfAHIAaQBjAGUAdwBwAG8AIAAqACAAdABfAHIAaQBjAGUAdwBwAG8AKQAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHIAaQBjAGUAIABjAHUAbAB0AGkAdgBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwByAGkAYwBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMASAA0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADcALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsAcgBpAGMAZQB9AD0AXABcAHMAdQBtAF8AdwBcAFwAcwB1AG0AXwBwAFwAXABzAHUAbQBfAG8AKABBAF8AewByAGkAYwBlACwAdwBwAG8AfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewByAGkAYwBlACwAdwBwAG8AfQBcAFwAdABpAG0AZQBzACAAdABfAHsAcgBpAGMAZQAsAHcAcABvAH0AKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAF8AcgBpAGMAZQB3AHAAbwBcACIALAAgAFwAIgBhAG4AbgB1AGEAbAAgAGEAcgBlAGEAIABvAGYAIAByAGkAYwBlACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuACAAdQBuAGQAZQByACAAdwBhAHQAZQByACAAcgBlAGcAaQBtAGUAIAB3ACwAIABwAHIAZQAtAHMAZQBhAHMAbwBuACAAdwBhAHQAZQByACAAcgBlAGcAaQBtAGUAIABwACwAIABhAG4AZAAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdAAgAGMAbwBuAGQAaQB0AGkAbwBuACAAbwBcACIALAAgAFwAIgBoAGEAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwByAGkAYwBlAHcAcABvAFwAIgAsACAAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAByAGkAYwBlACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuACAAdQBuAGQAZQByACAAYwBvAG4AZABpAHQAaQBvAG4AcwAgAHcALAAgAHAALAAgAGEAbgBkACAAbwBcACIALAAgAFwAIgBrAGcAIABDAEgANAAvAGgAYQAvAGQAYQB5AFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANwAuADEALgAxAC4AMQAsACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHQAXwByAGkAYwBlAHcAcABvAFwAIgAsACAAXAAiAGMAdQBsAHQAaQB2AGEAdABpAG8AbgAgAHAAZQByAGkAbwBkACAAZgBvAHIAIAByAGkAYwBlACAAdQBuAGQAZQByACAAYwBvAG4AZABpAHQAaQBvAG4AcwAgAHcALAAgAHAALAAgAGEAbgBkACAAbwBcACIALAAgAFwAIgBkAGEAeQBzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcwBcACIALAAgAFwAIgBuAHUAbQBiAGUAcgAgAG8AZgAgAGMAcgBvAHAAcABpAG4AZwAgAHMAZQBhAHMAbwBuAHMAIABpAG4AIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAbQBhAG4AYQBnAGUAZAAgAHQAaABpAHMAIAB3AGEAeQBcACIALAAgAFwAIgBzAGUAYQBzAG8AbgBzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAbgB1AG0AYgBlAHIAIABvAGYAIABzAGUAYQBzAG8AbgBzAFwAdQAwADAAMgA3ACAAdgBhAHIAaQBhAGIAbABlACAAYQBzACAAcABlAHIAIABWAEUARQBSAEcAIABkAGUAcwBjAHIAaQBwAHQAaQBvAG4AIABpAG4AIAA3AC4AMgAuADEAIABcAHUAMAAwADIANwBXAGgAZQByAGUAIAB0AGgAZQByAGUAIABpAHMAIABtAG8AcgBlACAAdABoAGEAbgAgAG8AbgBlACAAYwByAG8AcABwAGkAbgBnACAAcwBlAGEAcwBvAG4AIABwAGUAcgAgAHkAZQBhAHIALAAgAEEAcgBpAGMAZQAsAHcAcABvACAAcwBoAGEAbABsACAAYgBlACAAcwBjAGEAbABlAGQAIABhAGMAYwBvAHIAZABpAG4AZwBsAHkAXAB1ADAAMAAyADcAXAAiACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAbgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcgBpAGMAZQAgAGMAdQBsAHQAaQB2AGEAdABpAG8AbgBcAG4ARQBGAF8AcgBpAGMAZQB3AHAAbwBcAG4AawBnACAAQwBIADQALwBoAGEALwBkAGEAeQBcAG4ARQBGAF8AewByAGkAYwBlACwAdwBwAG8AfQA9AEUARgBfAGMAXABcAHQAaQBtAGUAcwAgAFMARgBfAHcAXABcAHQAaQBtAGUAcwAgAFMARgBfAHAAXABcAHQAaQBtAGUAcwAgAFMARgBfAG8AXABuAEUARgBfAGMAIAA9ACAAYgBhAHMAZQBsAGkAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGMAbwBuAHQAaQBuAHUAbwB1AHMAbAB5ACAAZgBsAG8AbwBkAGUAZAAgAGYAaQBlAGwAZABzACAAdwBpAHQAaABvAHUAdAAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdABzACAAKABrAGcAIABDAEgANAAvAGgAYQAvAGQAYQB5ACkAXABuAFMARgBfAHcAIAA9ACAAcwBjAGEAbABpAG4AZwAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAGQAdQByAGkAbgBnACAAdABoAGUAIABnAHIAbwB3AGkAbgBnACAAcwBlAGEAcwBvAG4AXABuAFMARgBfAHAAIAA9ACAAcwBjAGEAbABpAG4AZwAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAGkAbgAgAHQAaABlACAAcAByAGUALQBzAGUAYQBzAG8AbgBcAG4AUwBGAF8AbwAgAD0AIABzAGMAYQBsAGkAbgBnACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAeQBwAGUAIABhAG4AZAAgAGEAbQBvAHUAbgB0ACAAbwBmACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0AHMAIAAoAHMAZQB0ACAAdABvACAAMQAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdQBzAGUAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUARgBfAGMALAAgAFMARgBfAHcALAAgAFMARgBfAHAALAAgAFMARgBfAG8ALABcAG4AIAAgACAAIABFAEYAXwBjACAAKgAgAFMARgBfAHcAIAAqACAAUwBGAF8AcAAgACoAIABTAEYAXwBvAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHIAaQBjAGUAIABjAHUAbAB0AGkAdgBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUARgBfAHIAaQBjAGUAdwBwAG8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABDAEgANAAvAGgAYQAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADcALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAF8AewByAGkAYwBlACwAdwBwAG8AfQA9AEUARgBfAGMAXABcAHQAaQBtAGUAcwAgAFMARgBfAHcAXABcAHQAaQBtAGUAcwAgAFMARgBfAHAAXABcAHQAaQBtAGUAcwAgAFMARgBfAG8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADcALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AYwBcACIALAAgAFwAIgBiAGEAcwBlAGwAaQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAYwBvAG4AdABpAG4AdQBvAHUAcwBsAHkAIABmAGwAbwBvAGQAZQBkACAAZgBpAGUAbABkAHMAIAB3AGkAdABoAG8AdQB0ACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0AHMAXAAiACwAIABcACIAawBnACAAQwBIADQALwBoAGEALwBkAGEAeQBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgBfAHcAXAAiACwAIABcACIAcwBjAGEAbABpAG4AZwAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAGQAdQByAGkAbgBnACAAdABoAGUAIABnAHIAbwB3AGkAbgBnACAAcwBlAGEAcwBvAG4AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBGAF8AcABcACIALAAgAFwAIgBzAGMAYQBsAGkAbgBnACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAaQBuACAAdABoAGUAIABwAHIAZQAtAHMAZQBhAHMAbwBuAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgBfAG8AXAAiACwAIABcACIAcwBjAGEAbABpAG4AZwAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHkAcABlACAAYQBuAGQAIABhAG0AbwB1AG4AdAAgAG8AZgAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdABzAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADcALgAxAC4AMQAuADEALAAgACgAMwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgB3AFwAIgAsACAAXAAiAHcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAZAB1AHIAaQBuAGcAIABnAHIAbwB3AGkAbgBnACAAcwBlAGEAcwBvAG4AXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBwAFwAIgAsACAAXAAiAHAAcgBlAC0AcwBlAGEAcwBvAG4AIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAG8AXAAiACwAIABcACIAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0AFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXABuAE8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdABzACAAcwBjAGEAbABpAG4AZwAgAGYAYQBjAHQAbwByAFwAbgBTAEYAXwBvAFwAbgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAbgBTAEYAXwBvAD0AKAAxACsAXABcAHMAdQBtAF8AbwAoAFIATwBBAF8AbwBcAFwAdABpAG0AZQBzACAAQwBGAE8AQQBfAG8AKQApAF4AewAwAC4ANQA5AH0AXABuAFIATwBBAF8AbwAgAD0AIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAByAGEAdABlACAAbwBmACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0ACAAbwAgACgAdABvAG4AbgBlAHMALwBoAGEAKQBcAG4AQwBGAE8AQQBfAG8AIAA9ACAAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAbwBmACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0ACAAbwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUgBPAEEAXwBvACwAIABDAEYATwBBAF8AbwAsAFwAbgAgACAAIAAgACgAMQAgACsAIABTAFUATQAoAFIATwBBAF8AbwAgACoAIABDAEYATwBBAF8AbwApACkAIABeACAAMAAuADUAOQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABSAE8AQQBfAG8AMQAsACAAQwBGAE8AQQBfAG8AMQAsACAAUgBPAEEAXwBvADIALAAgAEMARgBPAEEAXwBvADIALAAgAFIATwBBAF8AbwAzACwAIABDAEYATwBBAF8AbwAzACwAIABSAE8AQQBfAG8ANAAsACAAQwBGAE8AQQBfAG8ANAAsACAAUgBPAEEAXwBvADUALAAgAEMARgBPAEEAXwBvADUALAAgAFIATwBBAF8AbwA2ACwAIABDAEYATwBBAF8AbwA2ACwAXABuACAAIAAgACAAKAAxACAAKwAgACgAKABSAE8AQQBfAG8AMQAgACoAIABDAEYATwBBAF8AbwAxACkAIAArACAAKABSAE8AQQBfAG8AMgAgACoAIABDAEYATwBBAF8AbwAyACkAIAArACAAKABSAE8AQQBfAG8AMwAgACoAIABDAEYATwBBAF8AbwAzACkAKwAgACgAUgBPAEEAXwBvADQAIAAqACAAQwBGAE8AQQBfAG8ANAApACAAKwAgACgAUgBPAEEAXwBvADUAIAAqACAAQwBGAE8AQQBfAG8ANQApACAAKwAgACgAUgBPAEEAXwBvADYAIAAqACAAQwBGAE8AQQBfAG8ANgApACkAKQAgAF4AIAAwAC4ANQA5AFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBPAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAcwAgAHMAYwBhAGwAaQBuAGcAIABmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBTAEYAXwBvAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANwAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAzACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAUwBGAF8AbwA9ACgAMQArAFwAXABzAHUAbQBfAG8AUgBPAEEAXwBvAFwAXAB0AGkAbQBlAHMAIABDAEYATwBBAF8AbwApAF4AewAwAC4ANQA5AH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMARgBfAG8APQAoADEAKwAgACgAKABSAE8AQQBfAG8AMQBcAFwAdABpAG0AZQBzACAAQwBGAE8AQQBfAG8AMQApACAAKwAgACgAUgBPAEEAXwBvADIAXABcAHQAaQBtAGUAcwAgAEMARgBPAEEAXwBvADIAKQAgACsAIAAoAFIATwBBAF8AbwAzAFwAXAB0AGkAbQBlAHMAIABDAEYATwBBAF8AbwAzACkAIAArACAAKABSAE8AQQBfAG8ANABcAFwAdABpAG0AZQBzACAAQwBGAE8AQQBfAG8ANAApACAAKwAgACgAUgBPAEEAXwBvADUAXABcAHQAaQBtAGUAcwAgAEMARgBPAEEAXwBvADUAKQAgACsAIAAoAFIATwBBAF8AbwA2AFwAXAB0AGkAbQBlAHMAIABDAEYATwBBAF8AbwA2ACkAKQBeAHsAMAAuADUAOQB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBPAEEAXwBvAFwAIgAsACAAXAAiAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHIAYQB0AGUAIABvAGYAIABvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAIABvAFwAIgAsACAAXAAiAHQAbwBuAG4AZQBzAC8AaABhAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBGAE8AQQBfAG8AXAAiACwAIABcACIAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAbwBmACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0ACAAbwBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBvAFwAIgAsACAAXAAiAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdAAgAHQAeQBwAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAGMAbAB1AGQAZQBkACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBzACAAYQBtAGUAbgBkAG0AZQBuAHQAIABhAHMAIABwAGUAcgAgAFYARQBFAFIARwAgAGUAcQB1AGEAdABpAG8AbgAgAGQAZQBzAGMAcgBpAHAAdABpAG8AbgA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGgAZQByAGUAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABpAHMAIABhAHAAcABsAGkAZQBkACAAdABvACAAdABoAGUAIAByAGkAYwBlACAAZgBpAGUAbABkAHMAIAByAGEAdABoAGUAcgAgAHQAaABhAG4AIABvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAcwAsACAAUwBGAF8AbwAgAGkAcwAgAHMAZQB0ACAAdABvACAAMQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGUAYwBsAGEAcgBlAGQAIABlAGEAYwBoACAAYQBtAGUAbgBkAG0AZQBuAHQAIABzAGUAcABhAHIAYQB0AGUAbAB5ACAAdABvACAAYQBsAGwAbwB3ACAAcwB1AG0AbQBpAG4AZwAgAGkAbgAgAEUAeABjAGUAbAAgAGkAbgAgAG8AbgBlACAAZQBxAHUAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgAiAH0AXQAsACIAcAByAG8AagBlAGMAdABOAGEAbQBlAHMAIgA6AFsAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AQQBwAHAAZQBuAGQAaQBjAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAEcAcgBvAHcAaQBuAGcAUwBlAGEAcwBvAG4AXwBVAG4AaQB0ACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAEcAcgBvAHcAaQBuAGcAUwBlAGEAcwBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAEQAYQB0AGEAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBUAGkAdABsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBVAG4AaQB0ACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBQAHIAZQBTAGUAYQBzAG8AbgBfAEQAYQB0AGEAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVABpAHQAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBVAG4AaQB0ACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFMAbwB1AHIAYwBlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAEQAYQB0AGEAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAFQAaQB0AGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEIAYQBzAGUAbABpAG4AZQBFAEYAXwBVAG4AaQB0ACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEIAYQBzAGUAbABpAG4AZQBFAEYAXwBTAG8AdQByAGMAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAEQAYQB0AGEAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBUAGkAdABsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AVQBuAGkAdAAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809E3D44-A88D-4EBF-A307-6B8CE77A3361}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -17058,23 +17078,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -17083,4 +17087,12 @@
     <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>